--- a/material/asistencia/Reporte-Asistencia-Ciclo-Formacion-Dataton-2026.xlsx
+++ b/material/asistencia/Reporte-Asistencia-Ciclo-Formacion-Dataton-2026.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OANGULO\Desktop\DATATON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\spacheco\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF454F4-E8E7-4899-99EA-1727FA95013B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13620"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -17,22 +18,32 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$5:$5</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Revisión automática</author>
   </authors>
   <commentList>
-    <comment ref="J6" authorId="0" shapeId="0">
+    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -46,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N6" authorId="0" shapeId="0">
+    <comment ref="N6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -60,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="0" shapeId="0">
+    <comment ref="P6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -74,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R6" authorId="0" shapeId="0">
+    <comment ref="R6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -88,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T6" authorId="0" shapeId="0">
+    <comment ref="T6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -102,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V6" authorId="0" shapeId="0">
+    <comment ref="V6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -116,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J30" authorId="0" shapeId="0">
+    <comment ref="J30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -130,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N30" authorId="0" shapeId="0">
+    <comment ref="N30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -144,7 +155,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V51" authorId="0" shapeId="0">
+    <comment ref="V51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -158,7 +169,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P52" authorId="0" shapeId="0">
+    <comment ref="P52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -172,7 +183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M60" authorId="0" shapeId="0">
+    <comment ref="M60" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -186,7 +197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V67" authorId="0" shapeId="0">
+    <comment ref="V67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -200,7 +211,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V68" authorId="0" shapeId="0">
+    <comment ref="V68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -214,7 +225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V69" authorId="0" shapeId="0">
+    <comment ref="V69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -228,7 +239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V75" authorId="0" shapeId="0">
+    <comment ref="V75" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -242,7 +253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N78" authorId="0" shapeId="0">
+    <comment ref="N78" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
         <r>
           <rPr>
@@ -256,7 +267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J79" authorId="0" shapeId="0">
+    <comment ref="J79" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
       <text>
         <r>
           <rPr>
@@ -270,7 +281,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N79" authorId="0" shapeId="0">
+    <comment ref="N79" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
       <text>
         <r>
           <rPr>
@@ -284,7 +295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V81" authorId="0" shapeId="0">
+    <comment ref="V81" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
       <text>
         <r>
           <rPr>
@@ -298,7 +309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N82" authorId="0" shapeId="0">
+    <comment ref="N82" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
       <text>
         <r>
           <rPr>
@@ -312,7 +323,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P82" authorId="0" shapeId="0">
+    <comment ref="P82" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
       <text>
         <r>
           <rPr>
@@ -326,7 +337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R82" authorId="0" shapeId="0">
+    <comment ref="R82" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
       <text>
         <r>
           <rPr>
@@ -340,7 +351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T82" authorId="0" shapeId="0">
+    <comment ref="T82" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
       <text>
         <r>
           <rPr>
@@ -354,7 +365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T84" authorId="0" shapeId="0">
+    <comment ref="T84" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
       <text>
         <r>
           <rPr>
@@ -368,7 +379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V93" authorId="0" shapeId="0">
+    <comment ref="V93" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
       <text>
         <r>
           <rPr>
@@ -382,7 +393,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N98" authorId="0" shapeId="0">
+    <comment ref="N98" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -396,7 +407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P98" authorId="0" shapeId="0">
+    <comment ref="P98" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -410,7 +421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V103" authorId="0" shapeId="0">
+    <comment ref="V103" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -424,7 +435,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T105" authorId="0" shapeId="0">
+    <comment ref="T105" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -438,7 +449,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V105" authorId="0" shapeId="0">
+    <comment ref="V105" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -452,7 +463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R108" authorId="0" shapeId="0">
+    <comment ref="R108" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -466,7 +477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V109" authorId="0" shapeId="0">
+    <comment ref="V109" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000020000000}">
       <text>
         <r>
           <rPr>
@@ -480,7 +491,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R111" authorId="0" shapeId="0">
+    <comment ref="R111" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000021000000}">
       <text>
         <r>
           <rPr>
@@ -494,7 +505,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T111" authorId="0" shapeId="0">
+    <comment ref="T111" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000022000000}">
       <text>
         <r>
           <rPr>
@@ -508,7 +519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V111" authorId="0" shapeId="0">
+    <comment ref="V111" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000023000000}">
       <text>
         <r>
           <rPr>
@@ -522,7 +533,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V128" authorId="0" shapeId="0">
+    <comment ref="V128" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000024000000}">
       <text>
         <r>
           <rPr>
@@ -536,7 +547,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V130" authorId="0" shapeId="0">
+    <comment ref="V130" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000025000000}">
       <text>
         <r>
           <rPr>
@@ -550,7 +561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q136" authorId="0" shapeId="0">
+    <comment ref="Q136" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000026000000}">
       <text>
         <r>
           <rPr>
@@ -564,7 +575,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J141" authorId="0" shapeId="0">
+    <comment ref="J141" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000027000000}">
       <text>
         <r>
           <rPr>
@@ -578,7 +589,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R141" authorId="0" shapeId="0">
+    <comment ref="R141" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000028000000}">
       <text>
         <r>
           <rPr>
@@ -592,7 +603,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T141" authorId="0" shapeId="0">
+    <comment ref="T141" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000029000000}">
       <text>
         <r>
           <rPr>
@@ -606,7 +617,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V141" authorId="0" shapeId="0">
+    <comment ref="V141" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002A000000}">
       <text>
         <r>
           <rPr>
@@ -620,7 +631,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V144" authorId="0" shapeId="0">
+    <comment ref="V144" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002B000000}">
       <text>
         <r>
           <rPr>
@@ -639,7 +650,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="218">
   <si>
     <t xml:space="preserve">                                    </t>
   </si>
@@ -1298,8 +1309,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1348,6 +1359,14 @@
       <b/>
       <sz val="16"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1595,7 +1614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1720,46 +1739,10 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1768,6 +1751,21 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1783,7 +1781,34 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1792,6 +1817,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF66FF66"/>
+      <color rgb="FF666699"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2065,13 +2096,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:AP164"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:AP153"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="12.75" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8" style="1" customWidth="1"/>
     <col min="4" max="4" width="36.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="26" width="12.140625" style="2" customWidth="1"/>
     <col min="27" max="27" width="14.42578125" style="2" customWidth="1"/>
@@ -2084,34 +2115,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:29" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="64" t="s">
         <v>217</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="2" spans="2:29" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="60" t="s">
         <v>215</v>
       </c>
-      <c r="D3" s="56" t="s">
+      <c r="D3" s="60" t="s">
         <v>214</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="59" t="s">
         <v>213</v>
       </c>
       <c r="F3" s="50"/>
       <c r="G3" s="50"/>
       <c r="H3" s="50"/>
-      <c r="I3" s="56" t="s">
+      <c r="I3" s="60" t="s">
         <v>212</v>
       </c>
       <c r="J3" s="50"/>
@@ -2119,7 +2150,7 @@
       <c r="L3" s="50"/>
       <c r="M3" s="50"/>
       <c r="N3" s="50"/>
-      <c r="O3" s="55" t="s">
+      <c r="O3" s="59" t="s">
         <v>211</v>
       </c>
       <c r="P3" s="50"/>
@@ -2127,28 +2158,28 @@
       <c r="R3" s="50"/>
       <c r="S3" s="50"/>
       <c r="T3" s="50"/>
-      <c r="U3" s="56" t="s">
+      <c r="U3" s="60" t="s">
         <v>210</v>
       </c>
       <c r="V3" s="50"/>
-      <c r="W3" s="55" t="s">
+      <c r="W3" s="59" t="s">
         <v>209</v>
       </c>
       <c r="X3" s="50"/>
       <c r="Y3" s="50"/>
       <c r="Z3" s="50"/>
-      <c r="AA3" s="62" t="s">
+      <c r="AA3" s="53" t="s">
         <v>208</v>
       </c>
-      <c r="AB3" s="63" t="s">
+      <c r="AB3" s="54" t="s">
         <v>207</v>
       </c>
-      <c r="AC3" s="64"/>
+      <c r="AC3" s="55"/>
     </row>
     <row r="4" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="53"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
       <c r="E4" s="49" t="s">
         <v>206</v>
       </c>
@@ -2157,15 +2188,15 @@
         <v>205</v>
       </c>
       <c r="H4" s="50"/>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="58" t="s">
         <v>204</v>
       </c>
       <c r="J4" s="50"/>
-      <c r="K4" s="51" t="s">
+      <c r="K4" s="58" t="s">
         <v>203</v>
       </c>
       <c r="L4" s="50"/>
-      <c r="M4" s="51" t="s">
+      <c r="M4" s="58" t="s">
         <v>202</v>
       </c>
       <c r="N4" s="50"/>
@@ -2181,7 +2212,7 @@
         <v>199</v>
       </c>
       <c r="T4" s="50"/>
-      <c r="U4" s="51" t="s">
+      <c r="U4" s="58" t="s">
         <v>198</v>
       </c>
       <c r="V4" s="50"/>
@@ -2193,14 +2224,14 @@
         <v>196</v>
       </c>
       <c r="Z4" s="50"/>
-      <c r="AA4" s="62"/>
-      <c r="AB4" s="65"/>
-      <c r="AC4" s="66"/>
+      <c r="AA4" s="53"/>
+      <c r="AB4" s="56"/>
+      <c r="AC4" s="57"/>
     </row>
     <row r="5" spans="2:29" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="54"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
       <c r="E5" s="31" t="s">
         <v>195</v>
       </c>
@@ -2267,7 +2298,7 @@
       <c r="Z5" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="AA5" s="62"/>
+      <c r="AA5" s="53"/>
       <c r="AB5" s="41" t="s">
         <v>193</v>
       </c>
@@ -2279,7 +2310,7 @@
       <c r="B6" s="29">
         <v>1</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="63" t="s">
         <v>191</v>
       </c>
       <c r="D6" s="30" t="s">
@@ -2348,13 +2379,13 @@
         <v>1</v>
       </c>
       <c r="AA6" s="29">
-        <f>COUNT(Z6,X6,V6,T6,R6,P6,N6,L6,J6,H6,F6)</f>
+        <f>COUNT(A6,X6,V6,T6,R6,P6,N6,L6,J6,H6,F6,Z6)</f>
         <v>11</v>
       </c>
       <c r="AB6" s="29">
         <v>30</v>
       </c>
-      <c r="AC6" s="67">
+      <c r="AC6" s="46">
         <f>(AB6+AB7)/2</f>
         <v>30</v>
       </c>
@@ -2363,7 +2394,7 @@
       <c r="B7" s="18">
         <v>2</v>
       </c>
-      <c r="C7" s="46"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="20" t="s">
         <v>189</v>
       </c>
@@ -2430,19 +2461,19 @@
         <v>1</v>
       </c>
       <c r="AA7" s="18">
-        <f t="shared" ref="AA7:AA70" si="0">COUNT(Z7,X7,V7,T7,R7,P7,N7,L7,J7,H7,F7)</f>
+        <f>COUNT(Z7,X7,V7,T7,R7,P7,N7,L7,J7,H7,F7)</f>
         <v>11</v>
       </c>
       <c r="AB7" s="18">
         <v>30</v>
       </c>
-      <c r="AC7" s="60"/>
+      <c r="AC7" s="44"/>
     </row>
     <row r="8" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="23">
         <v>3</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="51" t="s">
         <v>188</v>
       </c>
       <c r="D8" s="27" t="s">
@@ -2481,7 +2512,9 @@
       <c r="S8" s="23"/>
       <c r="T8" s="23"/>
       <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
+      <c r="V8" s="29">
+        <v>1</v>
+      </c>
       <c r="W8" s="23"/>
       <c r="X8" s="23"/>
       <c r="Y8" s="23"/>
@@ -2489,13 +2522,13 @@
         <v>1</v>
       </c>
       <c r="AA8" s="6">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>COUNT(Z8,X8,V8,T8,R8,P8,N8,L8,J8,H8,F8)</f>
+        <v>5</v>
       </c>
       <c r="AB8" s="6">
         <v>10.8</v>
       </c>
-      <c r="AC8" s="61">
+      <c r="AC8" s="45">
         <f>(AB8+AB9)/2</f>
         <v>13.15</v>
       </c>
@@ -2504,7 +2537,7 @@
       <c r="B9" s="23">
         <v>4</v>
       </c>
-      <c r="C9" s="48"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="25" t="s">
         <v>186</v>
       </c>
@@ -2543,7 +2576,9 @@
       <c r="S9" s="23"/>
       <c r="T9" s="23"/>
       <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
+      <c r="V9" s="18">
+        <v>1</v>
+      </c>
       <c r="W9" s="23"/>
       <c r="X9" s="23"/>
       <c r="Y9" s="23"/>
@@ -2551,19 +2586,19 @@
         <v>1</v>
       </c>
       <c r="AA9" s="6">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f t="shared" ref="AA9:AA70" si="0">COUNT(Z9,X9,V9,T9,R9,P9,N9,L9,J9,H9,F9)</f>
+        <v>7</v>
       </c>
       <c r="AB9" s="6">
         <v>15.5</v>
       </c>
-      <c r="AC9" s="61"/>
+      <c r="AC9" s="45"/>
     </row>
     <row r="10" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <v>5</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="47" t="s">
         <v>185</v>
       </c>
       <c r="D10" s="22" t="s">
@@ -2618,7 +2653,7 @@
       <c r="U10" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V10" s="18">
+      <c r="V10" s="29">
         <v>1</v>
       </c>
       <c r="W10" s="18"/>
@@ -2630,13 +2665,13 @@
         <v>1</v>
       </c>
       <c r="AA10" s="18">
-        <f t="shared" si="0"/>
+        <f>COUNT(Z10,X10,V10,T10,R10,P10,N10,L10,J10,H10,F10)</f>
         <v>11</v>
       </c>
       <c r="AB10" s="18">
         <v>30</v>
       </c>
-      <c r="AC10" s="60">
+      <c r="AC10" s="44">
         <f>(AB10+AB11+AB12+AB13)/4</f>
         <v>9.5250000000000021</v>
       </c>
@@ -2645,7 +2680,7 @@
       <c r="B11" s="18">
         <v>6</v>
       </c>
-      <c r="C11" s="46"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="20" t="s">
         <v>183</v>
       </c>
@@ -2670,7 +2705,9 @@
       <c r="S11" s="18"/>
       <c r="T11" s="18"/>
       <c r="U11" s="18"/>
-      <c r="V11" s="18"/>
+      <c r="V11" s="18">
+        <v>1</v>
+      </c>
       <c r="W11" s="18"/>
       <c r="X11" s="18"/>
       <c r="Y11" s="18"/>
@@ -2678,19 +2715,19 @@
         <v>1</v>
       </c>
       <c r="AA11" s="18">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>COUNT(Z11,X11,V11,T11,R11,P11,N11,L11,J11,H11,F11)</f>
+        <v>2</v>
       </c>
       <c r="AB11" s="18">
         <v>2.7</v>
       </c>
-      <c r="AC11" s="60"/>
+      <c r="AC11" s="44"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <v>7</v>
       </c>
-      <c r="C12" s="46"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="20" t="s">
         <v>182</v>
       </c>
@@ -2723,7 +2760,9 @@
       <c r="U12" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V12" s="18"/>
+      <c r="V12" s="29">
+        <v>1</v>
+      </c>
       <c r="W12" s="18"/>
       <c r="X12" s="18"/>
       <c r="Y12" s="18"/>
@@ -2732,18 +2771,18 @@
       </c>
       <c r="AA12" s="18">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB12" s="18">
         <v>2.7</v>
       </c>
-      <c r="AC12" s="60"/>
+      <c r="AC12" s="44"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <v>8</v>
       </c>
-      <c r="C13" s="46"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="20" t="s">
         <v>181</v>
       </c>
@@ -2770,7 +2809,9 @@
       <c r="U13" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V13" s="18"/>
+      <c r="V13" s="18">
+        <v>1</v>
+      </c>
       <c r="W13" s="18"/>
       <c r="X13" s="18"/>
       <c r="Y13" s="18"/>
@@ -2779,18 +2820,18 @@
       </c>
       <c r="AA13" s="18">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB13" s="18">
         <v>2.7</v>
       </c>
-      <c r="AC13" s="60"/>
+      <c r="AC13" s="44"/>
     </row>
     <row r="14" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="6">
         <v>9</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="65" t="s">
         <v>180</v>
       </c>
       <c r="D14" s="17" t="s">
@@ -2813,7 +2854,9 @@
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
       <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
+      <c r="V14" s="29">
+        <v>1</v>
+      </c>
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
       <c r="Y14" s="6"/>
@@ -2822,12 +2865,12 @@
       </c>
       <c r="AA14" s="6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB14" s="6">
         <v>2.7</v>
       </c>
-      <c r="AC14" s="61">
+      <c r="AC14" s="45">
         <f>(AB14+AB15)/2</f>
         <v>2.7</v>
       </c>
@@ -2836,7 +2879,7 @@
       <c r="B15" s="6">
         <v>10</v>
       </c>
-      <c r="C15" s="44"/>
+      <c r="C15" s="66"/>
       <c r="D15" s="15" t="s">
         <v>178</v>
       </c>
@@ -2857,7 +2900,9 @@
       <c r="S15" s="6"/>
       <c r="T15" s="6"/>
       <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
+      <c r="V15" s="18">
+        <v>1</v>
+      </c>
       <c r="W15" s="6"/>
       <c r="X15" s="6"/>
       <c r="Y15" s="6"/>
@@ -2866,18 +2911,18 @@
       </c>
       <c r="AA15" s="6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB15" s="6">
         <v>2.7</v>
       </c>
-      <c r="AC15" s="61"/>
+      <c r="AC15" s="45"/>
     </row>
     <row r="16" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <v>11</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="47" t="s">
         <v>177</v>
       </c>
       <c r="D16" s="22" t="s">
@@ -2928,7 +2973,7 @@
       <c r="U16" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V16" s="18">
+      <c r="V16" s="29">
         <v>1</v>
       </c>
       <c r="W16" s="18"/>
@@ -2946,7 +2991,7 @@
       <c r="AB16" s="18">
         <v>21.9</v>
       </c>
-      <c r="AC16" s="60">
+      <c r="AC16" s="44">
         <f>(AB16+AB17+AB18+AB19)/4</f>
         <v>21.824999999999999</v>
       </c>
@@ -2955,7 +3000,7 @@
       <c r="B17" s="18">
         <v>12</v>
       </c>
-      <c r="C17" s="46"/>
+      <c r="C17" s="48"/>
       <c r="D17" s="20" t="s">
         <v>175</v>
       </c>
@@ -3000,7 +3045,9 @@
       <c r="U17" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V17" s="18"/>
+      <c r="V17" s="18">
+        <v>1</v>
+      </c>
       <c r="W17" s="18"/>
       <c r="X17" s="18"/>
       <c r="Y17" s="18"/>
@@ -3009,18 +3056,18 @@
       </c>
       <c r="AA17" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB17" s="18">
         <v>10.8</v>
       </c>
-      <c r="AC17" s="60"/>
+      <c r="AC17" s="44"/>
     </row>
     <row r="18" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <v>13</v>
       </c>
-      <c r="C18" s="46"/>
+      <c r="C18" s="48"/>
       <c r="D18" s="20" t="s">
         <v>174</v>
       </c>
@@ -3073,7 +3120,7 @@
       <c r="U18" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V18" s="18">
+      <c r="V18" s="29">
         <v>1</v>
       </c>
       <c r="W18" s="18"/>
@@ -3085,19 +3132,19 @@
         <v>1</v>
       </c>
       <c r="AA18" s="18">
-        <f t="shared" si="0"/>
+        <f>COUNT(Z18,X18,V18,T18,R18,P18,N18,L18,J18,H18,F18)</f>
         <v>10</v>
       </c>
       <c r="AB18" s="18">
         <v>27.3</v>
       </c>
-      <c r="AC18" s="60"/>
+      <c r="AC18" s="44"/>
     </row>
     <row r="19" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <v>14</v>
       </c>
-      <c r="C19" s="46"/>
+      <c r="C19" s="48"/>
       <c r="D19" s="20" t="s">
         <v>173</v>
       </c>
@@ -3168,13 +3215,13 @@
       <c r="AB19" s="18">
         <v>27.3</v>
       </c>
-      <c r="AC19" s="60"/>
+      <c r="AC19" s="44"/>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B20" s="23">
         <v>15</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="51" t="s">
         <v>172</v>
       </c>
       <c r="D20" s="27" t="s">
@@ -3221,21 +3268,25 @@
       <c r="S20" s="23"/>
       <c r="T20" s="23"/>
       <c r="U20" s="23"/>
-      <c r="V20" s="23"/>
+      <c r="V20" s="29">
+        <v>1</v>
+      </c>
       <c r="W20" s="23"/>
-      <c r="X20" s="23"/>
+      <c r="X20" s="42">
+        <v>1</v>
+      </c>
       <c r="Y20" s="23"/>
       <c r="Z20" s="23">
         <v>1</v>
       </c>
       <c r="AA20" s="23">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>COUNT(Z20,X20,V20,T20,R20,P20,N20,L20,J20,H20,F20)</f>
+        <v>8</v>
       </c>
       <c r="AB20" s="23">
         <v>15.5</v>
       </c>
-      <c r="AC20" s="61">
+      <c r="AC20" s="45">
         <f>(AB20+AB21)/2</f>
         <v>13.15</v>
       </c>
@@ -3244,7 +3295,7 @@
       <c r="B21" s="23">
         <v>16</v>
       </c>
-      <c r="C21" s="48"/>
+      <c r="C21" s="52"/>
       <c r="D21" s="25" t="s">
         <v>170</v>
       </c>
@@ -3277,7 +3328,9 @@
       <c r="O21" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="P21" s="23"/>
+      <c r="P21" s="42">
+        <v>1</v>
+      </c>
       <c r="Q21" s="33" t="s">
         <v>1</v>
       </c>
@@ -3285,7 +3338,9 @@
       <c r="S21" s="23"/>
       <c r="T21" s="23"/>
       <c r="U21" s="23"/>
-      <c r="V21" s="23"/>
+      <c r="V21" s="18">
+        <v>1</v>
+      </c>
       <c r="W21" s="23"/>
       <c r="X21" s="23"/>
       <c r="Y21" s="23"/>
@@ -3294,18 +3349,18 @@
       </c>
       <c r="AA21" s="23">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AB21" s="23">
         <v>10.8</v>
       </c>
-      <c r="AC21" s="61"/>
+      <c r="AC21" s="45"/>
     </row>
     <row r="22" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <v>17</v>
       </c>
-      <c r="C22" s="45" t="s">
+      <c r="C22" s="47" t="s">
         <v>169</v>
       </c>
       <c r="D22" s="22" t="s">
@@ -3352,7 +3407,9 @@
       <c r="S22" s="18"/>
       <c r="T22" s="18"/>
       <c r="U22" s="18"/>
-      <c r="V22" s="18"/>
+      <c r="V22" s="29">
+        <v>1</v>
+      </c>
       <c r="W22" s="18"/>
       <c r="X22" s="18"/>
       <c r="Y22" s="18"/>
@@ -3361,12 +3418,12 @@
       </c>
       <c r="AA22" s="18">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB22" s="18">
         <v>19.2</v>
       </c>
-      <c r="AC22" s="60">
+      <c r="AC22" s="44">
         <f>(AB22+AB23+AB24)/3</f>
         <v>20.999999999999996</v>
       </c>
@@ -3375,7 +3432,7 @@
       <c r="B23" s="18">
         <v>18</v>
       </c>
-      <c r="C23" s="46"/>
+      <c r="C23" s="48"/>
       <c r="D23" s="20" t="s">
         <v>167</v>
       </c>
@@ -3424,7 +3481,9 @@
       <c r="S23" s="18"/>
       <c r="T23" s="18"/>
       <c r="U23" s="18"/>
-      <c r="V23" s="18"/>
+      <c r="V23" s="18">
+        <v>1</v>
+      </c>
       <c r="W23" s="18"/>
       <c r="X23" s="18"/>
       <c r="Y23" s="18"/>
@@ -3433,18 +3492,18 @@
       </c>
       <c r="AA23" s="18">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB23" s="18">
         <v>21.9</v>
       </c>
-      <c r="AC23" s="60"/>
+      <c r="AC23" s="44"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <v>19</v>
       </c>
-      <c r="C24" s="46"/>
+      <c r="C24" s="48"/>
       <c r="D24" s="20" t="s">
         <v>166</v>
       </c>
@@ -3493,7 +3552,9 @@
       <c r="S24" s="18"/>
       <c r="T24" s="18"/>
       <c r="U24" s="18"/>
-      <c r="V24" s="18"/>
+      <c r="V24" s="29">
+        <v>1</v>
+      </c>
       <c r="W24" s="18"/>
       <c r="X24" s="18"/>
       <c r="Y24" s="18"/>
@@ -3502,18 +3563,18 @@
       </c>
       <c r="AA24" s="18">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB24" s="18">
         <v>21.9</v>
       </c>
-      <c r="AC24" s="60"/>
+      <c r="AC24" s="44"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B25" s="23">
         <v>20</v>
       </c>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="51" t="s">
         <v>165</v>
       </c>
       <c r="D25" s="27" t="s">
@@ -3556,7 +3617,9 @@
       <c r="U25" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V25" s="23"/>
+      <c r="V25" s="18">
+        <v>1</v>
+      </c>
       <c r="W25" s="23"/>
       <c r="X25" s="23"/>
       <c r="Y25" s="23"/>
@@ -3565,12 +3628,12 @@
       </c>
       <c r="AA25" s="23">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB25" s="23">
         <v>8.1</v>
       </c>
-      <c r="AC25" s="61">
+      <c r="AC25" s="45">
         <f>(AB25+AB26+AB27+AB28)/4</f>
         <v>11.55</v>
       </c>
@@ -3579,7 +3642,7 @@
       <c r="B26" s="23">
         <v>21</v>
       </c>
-      <c r="C26" s="48"/>
+      <c r="C26" s="52"/>
       <c r="D26" s="25" t="s">
         <v>163</v>
       </c>
@@ -3628,7 +3691,7 @@
       <c r="U26" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V26" s="23">
+      <c r="V26" s="29">
         <v>1</v>
       </c>
       <c r="W26" s="23"/>
@@ -3646,13 +3709,13 @@
       <c r="AB26" s="23">
         <v>24.6</v>
       </c>
-      <c r="AC26" s="61"/>
+      <c r="AC26" s="45"/>
     </row>
     <row r="27" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="23">
         <v>22</v>
       </c>
-      <c r="C27" s="48"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="25" t="s">
         <v>162</v>
       </c>
@@ -3677,7 +3740,9 @@
       <c r="S27" s="23"/>
       <c r="T27" s="23"/>
       <c r="U27" s="23"/>
-      <c r="V27" s="23"/>
+      <c r="V27" s="18">
+        <v>1</v>
+      </c>
       <c r="W27" s="23"/>
       <c r="X27" s="23"/>
       <c r="Y27" s="23"/>
@@ -3686,18 +3751,18 @@
       </c>
       <c r="AA27" s="23">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB27" s="23">
         <v>5.4</v>
       </c>
-      <c r="AC27" s="61"/>
+      <c r="AC27" s="45"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B28" s="23">
         <v>23</v>
       </c>
-      <c r="C28" s="48"/>
+      <c r="C28" s="52"/>
       <c r="D28" s="25" t="s">
         <v>161</v>
       </c>
@@ -3734,7 +3799,9 @@
       <c r="S28" s="23"/>
       <c r="T28" s="23"/>
       <c r="U28" s="23"/>
-      <c r="V28" s="23"/>
+      <c r="V28" s="29">
+        <v>1</v>
+      </c>
       <c r="W28" s="23"/>
       <c r="X28" s="23"/>
       <c r="Y28" s="23"/>
@@ -3743,18 +3810,18 @@
       </c>
       <c r="AA28" s="23">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB28" s="23">
         <v>8.1</v>
       </c>
-      <c r="AC28" s="61"/>
+      <c r="AC28" s="45"/>
     </row>
     <row r="29" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <v>24</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="C29" s="47" t="s">
         <v>160</v>
       </c>
       <c r="D29" s="22" t="s">
@@ -3797,7 +3864,9 @@
         <v>1</v>
       </c>
       <c r="U29" s="18"/>
-      <c r="V29" s="18"/>
+      <c r="V29" s="18">
+        <v>1</v>
+      </c>
       <c r="W29" s="18"/>
       <c r="X29" s="18"/>
       <c r="Y29" s="18"/>
@@ -3806,12 +3875,12 @@
       </c>
       <c r="AA29" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB29" s="18">
         <v>10.8</v>
       </c>
-      <c r="AC29" s="60">
+      <c r="AC29" s="44">
         <f>(AB29+AB30)/2</f>
         <v>15</v>
       </c>
@@ -3820,7 +3889,7 @@
       <c r="B30" s="18">
         <v>25</v>
       </c>
-      <c r="C30" s="46"/>
+      <c r="C30" s="48"/>
       <c r="D30" s="20" t="s">
         <v>158</v>
       </c>
@@ -3867,7 +3936,9 @@
       </c>
       <c r="T30" s="18"/>
       <c r="U30" s="18"/>
-      <c r="V30" s="18"/>
+      <c r="V30" s="29">
+        <v>1</v>
+      </c>
       <c r="W30" s="18"/>
       <c r="X30" s="18"/>
       <c r="Y30" s="18"/>
@@ -3876,18 +3947,18 @@
       </c>
       <c r="AA30" s="18">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB30" s="18">
         <v>19.2</v>
       </c>
-      <c r="AC30" s="60"/>
+      <c r="AC30" s="44"/>
     </row>
     <row r="31" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="23">
         <v>26</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="51" t="s">
         <v>157</v>
       </c>
       <c r="D31" s="27" t="s">
@@ -3932,7 +4003,9 @@
       </c>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
+      <c r="V31" s="29">
+        <v>1</v>
+      </c>
       <c r="W31" s="23"/>
       <c r="X31" s="23"/>
       <c r="Y31" s="23"/>
@@ -3941,12 +4014,12 @@
       </c>
       <c r="AA31" s="23">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB31" s="23">
         <v>15.5</v>
       </c>
-      <c r="AC31" s="61">
+      <c r="AC31" s="45">
         <f>(AB31+AB32+AB33+AB34)/4</f>
         <v>11.3</v>
       </c>
@@ -3955,7 +4028,7 @@
       <c r="B32" s="23">
         <v>27</v>
       </c>
-      <c r="C32" s="48"/>
+      <c r="C32" s="52"/>
       <c r="D32" s="25" t="s">
         <v>155</v>
       </c>
@@ -3992,7 +4065,9 @@
       </c>
       <c r="T32" s="23"/>
       <c r="U32" s="23"/>
-      <c r="V32" s="23"/>
+      <c r="V32" s="18">
+        <v>1</v>
+      </c>
       <c r="W32" s="23"/>
       <c r="X32" s="23"/>
       <c r="Y32" s="23"/>
@@ -4001,18 +4076,18 @@
       </c>
       <c r="AA32" s="23">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB32" s="23">
         <v>5.4</v>
       </c>
-      <c r="AC32" s="61"/>
+      <c r="AC32" s="45"/>
     </row>
     <row r="33" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="23">
         <v>28</v>
       </c>
-      <c r="C33" s="48"/>
+      <c r="C33" s="52"/>
       <c r="D33" s="25" t="s">
         <v>154</v>
       </c>
@@ -4053,7 +4128,9 @@
         <v>1</v>
       </c>
       <c r="U33" s="23"/>
-      <c r="V33" s="23"/>
+      <c r="V33" s="29">
+        <v>1</v>
+      </c>
       <c r="W33" s="23"/>
       <c r="X33" s="23"/>
       <c r="Y33" s="23"/>
@@ -4062,18 +4139,18 @@
       </c>
       <c r="AA33" s="23">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB33" s="23">
         <v>13.5</v>
       </c>
-      <c r="AC33" s="61"/>
+      <c r="AC33" s="45"/>
     </row>
     <row r="34" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="23">
         <v>29</v>
       </c>
-      <c r="C34" s="48"/>
+      <c r="C34" s="52"/>
       <c r="D34" s="25" t="s">
         <v>153</v>
       </c>
@@ -4114,7 +4191,9 @@
       </c>
       <c r="T34" s="23"/>
       <c r="U34" s="23"/>
-      <c r="V34" s="23"/>
+      <c r="V34" s="18">
+        <v>1</v>
+      </c>
       <c r="W34" s="23"/>
       <c r="X34" s="23"/>
       <c r="Y34" s="23"/>
@@ -4123,18 +4202,18 @@
       </c>
       <c r="AA34" s="23">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB34" s="23">
         <v>10.8</v>
       </c>
-      <c r="AC34" s="61"/>
+      <c r="AC34" s="45"/>
     </row>
     <row r="35" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18">
         <v>30</v>
       </c>
-      <c r="C35" s="45" t="s">
+      <c r="C35" s="47" t="s">
         <v>152</v>
       </c>
       <c r="D35" s="22" t="s">
@@ -4161,7 +4240,9 @@
       <c r="S35" s="18"/>
       <c r="T35" s="18"/>
       <c r="U35" s="18"/>
-      <c r="V35" s="18"/>
+      <c r="V35" s="29">
+        <v>1</v>
+      </c>
       <c r="W35" s="18"/>
       <c r="X35" s="18"/>
       <c r="Y35" s="18"/>
@@ -4170,12 +4251,12 @@
       </c>
       <c r="AA35" s="18">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB35" s="18">
         <v>5.4</v>
       </c>
-      <c r="AC35" s="60">
+      <c r="AC35" s="44">
         <f>(AB35+AB36)/2</f>
         <v>4.0500000000000007</v>
       </c>
@@ -4184,7 +4265,7 @@
       <c r="B36" s="18">
         <v>31</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="48"/>
       <c r="D36" s="20" t="s">
         <v>150</v>
       </c>
@@ -4205,7 +4286,9 @@
       <c r="S36" s="18"/>
       <c r="T36" s="18"/>
       <c r="U36" s="18"/>
-      <c r="V36" s="18"/>
+      <c r="V36" s="18">
+        <v>1</v>
+      </c>
       <c r="W36" s="18"/>
       <c r="X36" s="18"/>
       <c r="Y36" s="18"/>
@@ -4214,18 +4297,18 @@
       </c>
       <c r="AA36" s="18">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB36" s="18">
         <v>2.7</v>
       </c>
-      <c r="AC36" s="60"/>
+      <c r="AC36" s="44"/>
     </row>
     <row r="37" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B37" s="23">
         <v>32</v>
       </c>
-      <c r="C37" s="47" t="s">
+      <c r="C37" s="51" t="s">
         <v>149</v>
       </c>
       <c r="D37" s="27" t="s">
@@ -4280,7 +4363,7 @@
       <c r="U37" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V37" s="23">
+      <c r="V37" s="29">
         <v>1</v>
       </c>
       <c r="W37" s="23"/>
@@ -4298,7 +4381,7 @@
       <c r="AB37" s="23">
         <v>30</v>
       </c>
-      <c r="AC37" s="61">
+      <c r="AC37" s="45">
         <f>(AB37+AB38+AB39+AB40)/4</f>
         <v>27.975000000000001</v>
       </c>
@@ -4307,7 +4390,7 @@
       <c r="B38" s="23">
         <v>33</v>
       </c>
-      <c r="C38" s="48"/>
+      <c r="C38" s="52"/>
       <c r="D38" s="25" t="s">
         <v>147</v>
       </c>
@@ -4350,15 +4433,21 @@
       <c r="Q38" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="R38" s="23"/>
+      <c r="R38" s="42">
+        <v>1</v>
+      </c>
       <c r="S38" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="T38" s="23"/>
+      <c r="T38" s="42">
+        <v>1</v>
+      </c>
       <c r="U38" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V38" s="23"/>
+      <c r="V38" s="18">
+        <v>1</v>
+      </c>
       <c r="W38" s="23"/>
       <c r="X38" s="23"/>
       <c r="Y38" s="23"/>
@@ -4367,18 +4456,18 @@
       </c>
       <c r="AA38" s="23">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB38" s="23">
         <v>27.3</v>
       </c>
-      <c r="AC38" s="61"/>
+      <c r="AC38" s="45"/>
     </row>
     <row r="39" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B39" s="23">
         <v>34</v>
       </c>
-      <c r="C39" s="48"/>
+      <c r="C39" s="52"/>
       <c r="D39" s="25" t="s">
         <v>146</v>
       </c>
@@ -4433,7 +4522,7 @@
       <c r="U39" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V39" s="23">
+      <c r="V39" s="29">
         <v>1</v>
       </c>
       <c r="W39" s="23"/>
@@ -4451,13 +4540,13 @@
       <c r="AB39" s="23">
         <v>30</v>
       </c>
-      <c r="AC39" s="61"/>
+      <c r="AC39" s="45"/>
     </row>
     <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" s="23">
         <v>35</v>
       </c>
-      <c r="C40" s="48"/>
+      <c r="C40" s="52"/>
       <c r="D40" s="25" t="s">
         <v>145</v>
       </c>
@@ -4510,7 +4599,9 @@
       <c r="U40" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V40" s="23"/>
+      <c r="V40" s="18">
+        <v>1</v>
+      </c>
       <c r="W40" s="23"/>
       <c r="X40" s="23">
         <v>1</v>
@@ -4521,18 +4612,18 @@
       </c>
       <c r="AA40" s="23">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB40" s="23">
         <v>24.6</v>
       </c>
-      <c r="AC40" s="61"/>
+      <c r="AC40" s="45"/>
     </row>
     <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" s="18">
         <v>36</v>
       </c>
-      <c r="C41" s="45" t="s">
+      <c r="C41" s="47" t="s">
         <v>144</v>
       </c>
       <c r="D41" s="22" t="s">
@@ -4577,7 +4668,9 @@
       <c r="U41" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V41" s="18"/>
+      <c r="V41" s="29">
+        <v>1</v>
+      </c>
       <c r="W41" s="18"/>
       <c r="X41" s="18"/>
       <c r="Y41" s="18"/>
@@ -4586,12 +4679,12 @@
       </c>
       <c r="AA41" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB41" s="18">
         <v>15.5</v>
       </c>
-      <c r="AC41" s="60">
+      <c r="AC41" s="44">
         <f>(AB41+AB42+AB43)/3</f>
         <v>15.5</v>
       </c>
@@ -4600,7 +4693,7 @@
       <c r="B42" s="18">
         <v>37</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="48"/>
       <c r="D42" s="20" t="s">
         <v>142</v>
       </c>
@@ -4657,13 +4750,13 @@
       <c r="AB42" s="18">
         <v>15.5</v>
       </c>
-      <c r="AC42" s="60"/>
+      <c r="AC42" s="44"/>
     </row>
     <row r="43" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B43" s="18">
         <v>38</v>
       </c>
-      <c r="C43" s="46"/>
+      <c r="C43" s="48"/>
       <c r="D43" s="20" t="s">
         <v>141</v>
       </c>
@@ -4704,7 +4797,7 @@
       <c r="U43" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V43" s="18">
+      <c r="V43" s="29">
         <v>1</v>
       </c>
       <c r="W43" s="18"/>
@@ -4720,13 +4813,13 @@
       <c r="AB43" s="18">
         <v>15.5</v>
       </c>
-      <c r="AC43" s="60"/>
+      <c r="AC43" s="44"/>
     </row>
     <row r="44" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B44" s="6">
         <v>39</v>
       </c>
-      <c r="C44" s="47" t="s">
+      <c r="C44" s="51" t="s">
         <v>140</v>
       </c>
       <c r="D44" s="27" t="s">
@@ -4773,7 +4866,9 @@
         <v>1</v>
       </c>
       <c r="U44" s="23"/>
-      <c r="V44" s="23"/>
+      <c r="V44" s="18">
+        <v>1</v>
+      </c>
       <c r="W44" s="23"/>
       <c r="X44" s="23"/>
       <c r="Y44" s="23"/>
@@ -4782,12 +4877,12 @@
       </c>
       <c r="AA44" s="23">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB44" s="23">
         <v>19.2</v>
       </c>
-      <c r="AC44" s="61">
+      <c r="AC44" s="45">
         <f>(AB44+AB45+AB46)/3</f>
         <v>10.899999999999999</v>
       </c>
@@ -4796,7 +4891,7 @@
       <c r="B45" s="6">
         <v>40</v>
       </c>
-      <c r="C45" s="48"/>
+      <c r="C45" s="52"/>
       <c r="D45" s="25" t="s">
         <v>138</v>
       </c>
@@ -4831,7 +4926,9 @@
       </c>
       <c r="T45" s="23"/>
       <c r="U45" s="23"/>
-      <c r="V45" s="23"/>
+      <c r="V45" s="29">
+        <v>1</v>
+      </c>
       <c r="W45" s="23"/>
       <c r="X45" s="23"/>
       <c r="Y45" s="23"/>
@@ -4840,23 +4937,27 @@
       </c>
       <c r="AA45" s="23">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB45" s="23">
         <v>8.1</v>
       </c>
-      <c r="AC45" s="61"/>
+      <c r="AC45" s="45"/>
     </row>
     <row r="46" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B46" s="6">
         <v>41</v>
       </c>
-      <c r="C46" s="48"/>
+      <c r="C46" s="52"/>
       <c r="D46" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
+      <c r="E46" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="42">
+        <v>1</v>
+      </c>
       <c r="G46" s="38"/>
       <c r="H46" s="23">
         <v>1</v>
@@ -4878,7 +4979,9 @@
       <c r="S46" s="23"/>
       <c r="T46" s="23"/>
       <c r="U46" s="23"/>
-      <c r="V46" s="23"/>
+      <c r="V46" s="18">
+        <v>1</v>
+      </c>
       <c r="W46" s="23"/>
       <c r="X46" s="23"/>
       <c r="Y46" s="23"/>
@@ -4887,18 +4990,18 @@
       </c>
       <c r="AA46" s="23">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB46" s="23">
         <v>5.4</v>
       </c>
-      <c r="AC46" s="61"/>
+      <c r="AC46" s="45"/>
     </row>
     <row r="47" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B47" s="18">
         <v>42</v>
       </c>
-      <c r="C47" s="45" t="s">
+      <c r="C47" s="47" t="s">
         <v>136</v>
       </c>
       <c r="D47" s="22" t="s">
@@ -4941,7 +5044,9 @@
       <c r="U47" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V47" s="18"/>
+      <c r="V47" s="29">
+        <v>1</v>
+      </c>
       <c r="W47" s="18"/>
       <c r="X47" s="18"/>
       <c r="Y47" s="18"/>
@@ -4950,12 +5055,12 @@
       </c>
       <c r="AA47" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB47" s="18">
         <v>10.8</v>
       </c>
-      <c r="AC47" s="60">
+      <c r="AC47" s="44">
         <f>(AB47+AB48+AB49+AB50)/4</f>
         <v>12.649999999999999</v>
       </c>
@@ -4964,7 +5069,7 @@
       <c r="B48" s="18">
         <v>43</v>
       </c>
-      <c r="C48" s="46"/>
+      <c r="C48" s="48"/>
       <c r="D48" s="20" t="s">
         <v>134</v>
       </c>
@@ -5009,7 +5114,9 @@
       <c r="U48" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V48" s="18"/>
+      <c r="V48" s="18">
+        <v>1</v>
+      </c>
       <c r="W48" s="18"/>
       <c r="X48" s="18">
         <v>1</v>
@@ -5020,18 +5127,18 @@
       </c>
       <c r="AA48" s="18">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB48" s="18">
         <v>15.5</v>
       </c>
-      <c r="AC48" s="60"/>
+      <c r="AC48" s="44"/>
     </row>
     <row r="49" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B49" s="18">
         <v>44</v>
       </c>
-      <c r="C49" s="46"/>
+      <c r="C49" s="48"/>
       <c r="D49" s="20" t="s">
         <v>133</v>
       </c>
@@ -5074,7 +5181,7 @@
       <c r="U49" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V49" s="18">
+      <c r="V49" s="29">
         <v>1</v>
       </c>
       <c r="W49" s="18"/>
@@ -5090,13 +5197,13 @@
       <c r="AB49" s="18">
         <v>13.5</v>
       </c>
-      <c r="AC49" s="60"/>
+      <c r="AC49" s="44"/>
     </row>
     <row r="50" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B50" s="18">
         <v>45</v>
       </c>
-      <c r="C50" s="46"/>
+      <c r="C50" s="48"/>
       <c r="D50" s="20" t="s">
         <v>132</v>
       </c>
@@ -5139,7 +5246,9 @@
       <c r="U50" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V50" s="18"/>
+      <c r="V50" s="18">
+        <v>1</v>
+      </c>
       <c r="W50" s="18"/>
       <c r="X50" s="18"/>
       <c r="Y50" s="18"/>
@@ -5148,18 +5257,18 @@
       </c>
       <c r="AA50" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB50" s="18">
         <v>10.8</v>
       </c>
-      <c r="AC50" s="60"/>
+      <c r="AC50" s="44"/>
     </row>
     <row r="51" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B51" s="6">
         <v>46</v>
       </c>
-      <c r="C51" s="47" t="s">
+      <c r="C51" s="51" t="s">
         <v>131</v>
       </c>
       <c r="D51" s="27" t="s">
@@ -5210,7 +5319,7 @@
       <c r="U51" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V51" s="23">
+      <c r="V51" s="29">
         <v>1</v>
       </c>
       <c r="W51" s="23"/>
@@ -5228,7 +5337,7 @@
       <c r="AB51" s="23">
         <v>27.3</v>
       </c>
-      <c r="AC51" s="61">
+      <c r="AC51" s="45">
         <f>(AB51+AB52)/2</f>
         <v>28.65</v>
       </c>
@@ -5237,7 +5346,7 @@
       <c r="B52" s="6">
         <v>47</v>
       </c>
-      <c r="C52" s="48"/>
+      <c r="C52" s="52"/>
       <c r="D52" s="25" t="s">
         <v>129</v>
       </c>
@@ -5292,7 +5401,7 @@
       <c r="U52" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V52" s="23">
+      <c r="V52" s="18">
         <v>1</v>
       </c>
       <c r="W52" s="23"/>
@@ -5310,13 +5419,13 @@
       <c r="AB52" s="23">
         <v>30</v>
       </c>
-      <c r="AC52" s="61"/>
+      <c r="AC52" s="45"/>
     </row>
     <row r="53" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="18">
         <v>48</v>
       </c>
-      <c r="C53" s="45" t="s">
+      <c r="C53" s="47" t="s">
         <v>128</v>
       </c>
       <c r="D53" s="22" t="s">
@@ -5361,7 +5470,7 @@
       <c r="U53" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V53" s="18">
+      <c r="V53" s="29">
         <v>1</v>
       </c>
       <c r="W53" s="18"/>
@@ -5379,7 +5488,7 @@
       <c r="AB53" s="18">
         <v>19.2</v>
       </c>
-      <c r="AC53" s="60">
+      <c r="AC53" s="44">
         <f>(AB53+AB54)/2</f>
         <v>20.549999999999997</v>
       </c>
@@ -5388,7 +5497,7 @@
       <c r="B54" s="18">
         <v>49</v>
       </c>
-      <c r="C54" s="46"/>
+      <c r="C54" s="48"/>
       <c r="D54" s="20" t="s">
         <v>126</v>
       </c>
@@ -5449,13 +5558,13 @@
       <c r="AB54" s="18">
         <v>21.9</v>
       </c>
-      <c r="AC54" s="60"/>
+      <c r="AC54" s="44"/>
     </row>
     <row r="55" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B55" s="6">
         <v>50</v>
       </c>
-      <c r="C55" s="47" t="s">
+      <c r="C55" s="51" t="s">
         <v>125</v>
       </c>
       <c r="D55" s="27" t="s">
@@ -5502,7 +5611,9 @@
         <v>1</v>
       </c>
       <c r="U55" s="23"/>
-      <c r="V55" s="23"/>
+      <c r="V55" s="29">
+        <v>1</v>
+      </c>
       <c r="W55" s="23"/>
       <c r="X55" s="23">
         <v>1</v>
@@ -5513,12 +5624,12 @@
       </c>
       <c r="AA55" s="23">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB55" s="23">
         <v>21.9</v>
       </c>
-      <c r="AC55" s="61">
+      <c r="AC55" s="45">
         <f>(AB55+AB56+AB57+AB58)/4</f>
         <v>17.524999999999999</v>
       </c>
@@ -5527,7 +5638,7 @@
       <c r="B56" s="6">
         <v>51</v>
       </c>
-      <c r="C56" s="48"/>
+      <c r="C56" s="52"/>
       <c r="D56" s="25" t="s">
         <v>123</v>
       </c>
@@ -5574,7 +5685,9 @@
         <v>1</v>
       </c>
       <c r="U56" s="23"/>
-      <c r="V56" s="23"/>
+      <c r="V56" s="18">
+        <v>1</v>
+      </c>
       <c r="W56" s="23"/>
       <c r="X56" s="23"/>
       <c r="Y56" s="23"/>
@@ -5583,18 +5696,18 @@
       </c>
       <c r="AA56" s="23">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB56" s="23">
         <v>19.2</v>
       </c>
-      <c r="AC56" s="61"/>
+      <c r="AC56" s="45"/>
     </row>
     <row r="57" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B57" s="6">
         <v>52</v>
       </c>
-      <c r="C57" s="48"/>
+      <c r="C57" s="52"/>
       <c r="D57" s="25" t="s">
         <v>122</v>
       </c>
@@ -5639,7 +5752,9 @@
         <v>1</v>
       </c>
       <c r="U57" s="23"/>
-      <c r="V57" s="23"/>
+      <c r="V57" s="29">
+        <v>1</v>
+      </c>
       <c r="W57" s="23"/>
       <c r="X57" s="23"/>
       <c r="Y57" s="23"/>
@@ -5648,18 +5763,18 @@
       </c>
       <c r="AA57" s="23">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB57" s="23">
         <v>15.5</v>
       </c>
-      <c r="AC57" s="61"/>
+      <c r="AC57" s="45"/>
     </row>
     <row r="58" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B58" s="6">
         <v>53</v>
       </c>
-      <c r="C58" s="48"/>
+      <c r="C58" s="52"/>
       <c r="D58" s="25" t="s">
         <v>121</v>
       </c>
@@ -5702,7 +5817,9 @@
       </c>
       <c r="T58" s="23"/>
       <c r="U58" s="23"/>
-      <c r="V58" s="23"/>
+      <c r="V58" s="18">
+        <v>1</v>
+      </c>
       <c r="W58" s="23"/>
       <c r="X58" s="23"/>
       <c r="Y58" s="23"/>
@@ -5711,18 +5828,18 @@
       </c>
       <c r="AA58" s="23">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB58" s="23">
         <v>13.5</v>
       </c>
-      <c r="AC58" s="61"/>
+      <c r="AC58" s="45"/>
     </row>
     <row r="59" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B59" s="18">
         <v>54</v>
       </c>
-      <c r="C59" s="45" t="s">
+      <c r="C59" s="47" t="s">
         <v>120</v>
       </c>
       <c r="D59" s="22" t="s">
@@ -5759,7 +5876,9 @@
       <c r="S59" s="18"/>
       <c r="T59" s="18"/>
       <c r="U59" s="18"/>
-      <c r="V59" s="18"/>
+      <c r="V59" s="29">
+        <v>1</v>
+      </c>
       <c r="W59" s="18"/>
       <c r="X59" s="18"/>
       <c r="Y59" s="18"/>
@@ -5768,12 +5887,12 @@
       </c>
       <c r="AA59" s="18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB59" s="18">
         <v>8.1</v>
       </c>
-      <c r="AC59" s="60">
+      <c r="AC59" s="44">
         <f>(AB59+AB60+AB61+AB62)/4</f>
         <v>8.7750000000000004</v>
       </c>
@@ -5782,7 +5901,7 @@
       <c r="B60" s="18">
         <v>55</v>
       </c>
-      <c r="C60" s="46"/>
+      <c r="C60" s="48"/>
       <c r="D60" s="20" t="s">
         <v>118</v>
       </c>
@@ -5819,7 +5938,9 @@
       <c r="S60" s="18"/>
       <c r="T60" s="18"/>
       <c r="U60" s="18"/>
-      <c r="V60" s="18"/>
+      <c r="V60" s="18">
+        <v>1</v>
+      </c>
       <c r="W60" s="18"/>
       <c r="X60" s="18"/>
       <c r="Y60" s="18"/>
@@ -5828,18 +5949,18 @@
       </c>
       <c r="AA60" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB60" s="18">
         <v>10.8</v>
       </c>
-      <c r="AC60" s="60"/>
+      <c r="AC60" s="44"/>
     </row>
     <row r="61" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B61" s="18">
         <v>56</v>
       </c>
-      <c r="C61" s="46"/>
+      <c r="C61" s="48"/>
       <c r="D61" s="20" t="s">
         <v>117</v>
       </c>
@@ -5874,7 +5995,9 @@
       <c r="S61" s="18"/>
       <c r="T61" s="18"/>
       <c r="U61" s="18"/>
-      <c r="V61" s="18"/>
+      <c r="V61" s="29">
+        <v>1</v>
+      </c>
       <c r="W61" s="18"/>
       <c r="X61" s="18"/>
       <c r="Y61" s="18"/>
@@ -5883,18 +6006,18 @@
       </c>
       <c r="AA61" s="18">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB61" s="18">
         <v>13.5</v>
       </c>
-      <c r="AC61" s="60"/>
+      <c r="AC61" s="44"/>
     </row>
     <row r="62" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B62" s="18">
         <v>57</v>
       </c>
-      <c r="C62" s="46"/>
+      <c r="C62" s="48"/>
       <c r="D62" s="20" t="s">
         <v>116</v>
       </c>
@@ -5923,7 +6046,9 @@
       <c r="S62" s="18"/>
       <c r="T62" s="18"/>
       <c r="U62" s="18"/>
-      <c r="V62" s="18"/>
+      <c r="V62" s="18">
+        <v>1</v>
+      </c>
       <c r="W62" s="18"/>
       <c r="X62" s="18"/>
       <c r="Y62" s="18"/>
@@ -5932,18 +6057,18 @@
       </c>
       <c r="AA62" s="18">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB62" s="18">
         <v>2.7</v>
       </c>
-      <c r="AC62" s="60"/>
+      <c r="AC62" s="44"/>
     </row>
     <row r="63" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="6">
         <v>58</v>
       </c>
-      <c r="C63" s="47" t="s">
+      <c r="C63" s="51" t="s">
         <v>115</v>
       </c>
       <c r="D63" s="27" t="s">
@@ -5966,7 +6091,9 @@
         <v>1</v>
       </c>
       <c r="K63" s="23"/>
-      <c r="L63" s="23"/>
+      <c r="L63" s="42">
+        <v>1</v>
+      </c>
       <c r="M63" s="23" t="s">
         <v>1</v>
       </c>
@@ -5988,7 +6115,9 @@
         <v>1</v>
       </c>
       <c r="U63" s="23"/>
-      <c r="V63" s="23"/>
+      <c r="V63" s="29">
+        <v>1</v>
+      </c>
       <c r="W63" s="23"/>
       <c r="X63" s="23">
         <v>1</v>
@@ -5999,12 +6128,12 @@
       </c>
       <c r="AA63" s="23">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AB63" s="23">
         <v>24.6</v>
       </c>
-      <c r="AC63" s="61">
+      <c r="AC63" s="45">
         <f>(AB63+AB64+AB65)/3</f>
         <v>23.7</v>
       </c>
@@ -6013,7 +6142,7 @@
       <c r="B64" s="6">
         <v>59</v>
       </c>
-      <c r="C64" s="48"/>
+      <c r="C64" s="52"/>
       <c r="D64" s="25" t="s">
         <v>113</v>
       </c>
@@ -6062,7 +6191,9 @@
       </c>
       <c r="T64" s="23"/>
       <c r="U64" s="23"/>
-      <c r="V64" s="23"/>
+      <c r="V64" s="18">
+        <v>1</v>
+      </c>
       <c r="W64" s="23"/>
       <c r="X64" s="23"/>
       <c r="Y64" s="23"/>
@@ -6071,18 +6202,18 @@
       </c>
       <c r="AA64" s="23">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB64" s="23">
         <v>19.2</v>
       </c>
-      <c r="AC64" s="61"/>
+      <c r="AC64" s="45"/>
     </row>
     <row r="65" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B65" s="6">
         <v>60</v>
       </c>
-      <c r="C65" s="48"/>
+      <c r="C65" s="52"/>
       <c r="D65" s="25" t="s">
         <v>112</v>
       </c>
@@ -6135,7 +6266,9 @@
         <v>1</v>
       </c>
       <c r="U65" s="23"/>
-      <c r="V65" s="23"/>
+      <c r="V65" s="29">
+        <v>1</v>
+      </c>
       <c r="W65" s="23"/>
       <c r="X65" s="23">
         <v>1</v>
@@ -6146,18 +6279,18 @@
       </c>
       <c r="AA65" s="23">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB65" s="23">
         <v>27.3</v>
       </c>
-      <c r="AC65" s="61"/>
+      <c r="AC65" s="45"/>
     </row>
     <row r="66" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="18">
         <v>61</v>
       </c>
-      <c r="C66" s="45" t="s">
+      <c r="C66" s="47" t="s">
         <v>111</v>
       </c>
       <c r="D66" s="22" t="s">
@@ -6194,7 +6327,9 @@
       <c r="U66" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V66" s="18"/>
+      <c r="V66" s="18">
+        <v>1</v>
+      </c>
       <c r="W66" s="18"/>
       <c r="X66" s="18"/>
       <c r="Y66" s="18"/>
@@ -6203,12 +6338,12 @@
       </c>
       <c r="AA66" s="18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB66" s="18">
         <v>8.1</v>
       </c>
-      <c r="AC66" s="60">
+      <c r="AC66" s="44">
         <f>(AB66+AB67+AB68+AB69)/4</f>
         <v>18.45</v>
       </c>
@@ -6217,7 +6352,7 @@
       <c r="B67" s="18">
         <v>62</v>
       </c>
-      <c r="C67" s="46"/>
+      <c r="C67" s="48"/>
       <c r="D67" s="20" t="s">
         <v>109</v>
       </c>
@@ -6266,7 +6401,7 @@
       <c r="U67" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V67" s="18">
+      <c r="V67" s="29">
         <v>1</v>
       </c>
       <c r="W67" s="18"/>
@@ -6282,13 +6417,13 @@
       <c r="AB67" s="18">
         <v>21.9</v>
       </c>
-      <c r="AC67" s="60"/>
+      <c r="AC67" s="44"/>
     </row>
     <row r="68" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B68" s="18">
         <v>63</v>
       </c>
-      <c r="C68" s="46"/>
+      <c r="C68" s="48"/>
       <c r="D68" s="20" t="s">
         <v>108</v>
       </c>
@@ -6355,13 +6490,13 @@
       <c r="AB68" s="18">
         <v>21.9</v>
       </c>
-      <c r="AC68" s="60"/>
+      <c r="AC68" s="44"/>
     </row>
     <row r="69" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B69" s="18">
         <v>64</v>
       </c>
-      <c r="C69" s="46"/>
+      <c r="C69" s="48"/>
       <c r="D69" s="20" t="s">
         <v>107</v>
       </c>
@@ -6412,7 +6547,7 @@
       <c r="U69" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V69" s="18">
+      <c r="V69" s="29">
         <v>1</v>
       </c>
       <c r="W69" s="18"/>
@@ -6428,13 +6563,13 @@
       <c r="AB69" s="18">
         <v>21.9</v>
       </c>
-      <c r="AC69" s="60"/>
+      <c r="AC69" s="44"/>
     </row>
     <row r="70" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B70" s="6">
         <v>65</v>
       </c>
-      <c r="C70" s="47" t="s">
+      <c r="C70" s="51" t="s">
         <v>106</v>
       </c>
       <c r="D70" s="27" t="s">
@@ -6491,7 +6626,7 @@
       <c r="U70" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="V70" s="23">
+      <c r="V70" s="29">
         <v>1</v>
       </c>
       <c r="W70" s="23"/>
@@ -6509,7 +6644,7 @@
       <c r="AB70" s="23">
         <v>30</v>
       </c>
-      <c r="AC70" s="61">
+      <c r="AC70" s="45">
         <f>(AB70+AB71)/2</f>
         <v>30</v>
       </c>
@@ -6518,7 +6653,7 @@
       <c r="B71" s="6">
         <v>66</v>
       </c>
-      <c r="C71" s="48"/>
+      <c r="C71" s="52"/>
       <c r="D71" s="25" t="s">
         <v>104</v>
       </c>
@@ -6573,7 +6708,7 @@
       <c r="U71" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V71" s="23">
+      <c r="V71" s="18">
         <v>1</v>
       </c>
       <c r="W71" s="23"/>
@@ -6591,13 +6726,13 @@
       <c r="AB71" s="23">
         <v>30</v>
       </c>
-      <c r="AC71" s="61"/>
+      <c r="AC71" s="45"/>
     </row>
     <row r="72" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B72" s="18">
         <v>67</v>
       </c>
-      <c r="C72" s="45" t="s">
+      <c r="C72" s="47" t="s">
         <v>103</v>
       </c>
       <c r="D72" s="22" t="s">
@@ -6650,7 +6785,7 @@
       <c r="U72" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V72" s="18">
+      <c r="V72" s="29">
         <v>1</v>
       </c>
       <c r="W72" s="18"/>
@@ -6668,7 +6803,7 @@
       <c r="AB72" s="18">
         <v>27.3</v>
       </c>
-      <c r="AC72" s="60">
+      <c r="AC72" s="44">
         <f>(AB72+AB73+AB74+AB75)/4</f>
         <v>25.024999999999999</v>
       </c>
@@ -6677,7 +6812,7 @@
       <c r="B73" s="18">
         <v>68</v>
       </c>
-      <c r="C73" s="46"/>
+      <c r="C73" s="48"/>
       <c r="D73" s="20" t="s">
         <v>101</v>
       </c>
@@ -6748,13 +6883,13 @@
       <c r="AB73" s="18">
         <v>30</v>
       </c>
-      <c r="AC73" s="60"/>
+      <c r="AC73" s="44"/>
     </row>
     <row r="74" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B74" s="18">
         <v>69</v>
       </c>
-      <c r="C74" s="46"/>
+      <c r="C74" s="48"/>
       <c r="D74" s="20" t="s">
         <v>100</v>
       </c>
@@ -6805,7 +6940,7 @@
       <c r="U74" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V74" s="18">
+      <c r="V74" s="29">
         <v>1</v>
       </c>
       <c r="W74" s="18"/>
@@ -6823,13 +6958,13 @@
       <c r="AB74" s="18">
         <v>27.3</v>
       </c>
-      <c r="AC74" s="60"/>
+      <c r="AC74" s="44"/>
     </row>
     <row r="75" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="18">
         <v>70</v>
       </c>
-      <c r="C75" s="46"/>
+      <c r="C75" s="48"/>
       <c r="D75" s="20" t="s">
         <v>99</v>
       </c>
@@ -6890,13 +7025,13 @@
       <c r="AB75" s="18">
         <v>15.5</v>
       </c>
-      <c r="AC75" s="60"/>
+      <c r="AC75" s="44"/>
     </row>
     <row r="76" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B76" s="6">
         <v>71</v>
       </c>
-      <c r="C76" s="47" t="s">
+      <c r="C76" s="51" t="s">
         <v>98</v>
       </c>
       <c r="D76" s="27" t="s">
@@ -6941,7 +7076,9 @@
       <c r="U76" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V76" s="23"/>
+      <c r="V76" s="29">
+        <v>1</v>
+      </c>
       <c r="W76" s="23"/>
       <c r="X76" s="23"/>
       <c r="Y76" s="23"/>
@@ -6950,12 +7087,12 @@
       </c>
       <c r="AA76" s="23">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB76" s="23">
         <v>10.8</v>
       </c>
-      <c r="AC76" s="61">
+      <c r="AC76" s="45">
         <f>(AB76+AB77+AB78)/3</f>
         <v>14.5</v>
       </c>
@@ -6964,7 +7101,7 @@
       <c r="B77" s="6">
         <v>72</v>
       </c>
-      <c r="C77" s="48"/>
+      <c r="C77" s="52"/>
       <c r="D77" s="25" t="s">
         <v>96</v>
       </c>
@@ -7013,7 +7150,7 @@
       <c r="U77" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V77" s="23">
+      <c r="V77" s="18">
         <v>1</v>
       </c>
       <c r="W77" s="23"/>
@@ -7031,13 +7168,13 @@
       <c r="AB77" s="23">
         <v>27.3</v>
       </c>
-      <c r="AC77" s="61"/>
+      <c r="AC77" s="45"/>
     </row>
     <row r="78" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B78" s="6">
         <v>73</v>
       </c>
-      <c r="C78" s="48"/>
+      <c r="C78" s="52"/>
       <c r="D78" s="25" t="s">
         <v>95</v>
       </c>
@@ -7076,7 +7213,9 @@
       <c r="U78" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V78" s="23"/>
+      <c r="V78" s="29">
+        <v>1</v>
+      </c>
       <c r="W78" s="23"/>
       <c r="X78" s="23"/>
       <c r="Y78" s="23"/>
@@ -7085,18 +7224,18 @@
       </c>
       <c r="AA78" s="23">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB78" s="23">
         <v>5.4</v>
       </c>
-      <c r="AC78" s="61"/>
+      <c r="AC78" s="45"/>
     </row>
     <row r="79" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B79" s="18">
         <v>74</v>
       </c>
-      <c r="C79" s="45" t="s">
+      <c r="C79" s="47" t="s">
         <v>94</v>
       </c>
       <c r="D79" s="22" t="s">
@@ -7135,7 +7274,9 @@
       <c r="S79" s="18"/>
       <c r="T79" s="18"/>
       <c r="U79" s="18"/>
-      <c r="V79" s="18"/>
+      <c r="V79" s="18">
+        <v>1</v>
+      </c>
       <c r="W79" s="18"/>
       <c r="X79" s="18"/>
       <c r="Y79" s="18"/>
@@ -7144,12 +7285,12 @@
       </c>
       <c r="AA79" s="18">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB79" s="18">
         <v>13.5</v>
       </c>
-      <c r="AC79" s="60">
+      <c r="AC79" s="44">
         <f>(AB79+AB80)/2</f>
         <v>13.5</v>
       </c>
@@ -7158,7 +7299,7 @@
       <c r="B80" s="18">
         <v>75</v>
       </c>
-      <c r="C80" s="46"/>
+      <c r="C80" s="48"/>
       <c r="D80" s="20" t="s">
         <v>92</v>
       </c>
@@ -7197,7 +7338,9 @@
       <c r="S80" s="18"/>
       <c r="T80" s="18"/>
       <c r="U80" s="18"/>
-      <c r="V80" s="18"/>
+      <c r="V80" s="29">
+        <v>1</v>
+      </c>
       <c r="W80" s="18"/>
       <c r="X80" s="18"/>
       <c r="Y80" s="18"/>
@@ -7206,18 +7349,18 @@
       </c>
       <c r="AA80" s="18">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB80" s="18">
         <v>13.5</v>
       </c>
-      <c r="AC80" s="60"/>
+      <c r="AC80" s="44"/>
     </row>
     <row r="81" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B81" s="6">
         <v>76</v>
       </c>
-      <c r="C81" s="47" t="s">
+      <c r="C81" s="51" t="s">
         <v>91</v>
       </c>
       <c r="D81" s="27" t="s">
@@ -7272,7 +7415,7 @@
       <c r="U81" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="V81" s="23">
+      <c r="V81" s="18">
         <v>1</v>
       </c>
       <c r="W81" s="23"/>
@@ -7290,7 +7433,7 @@
       <c r="AB81" s="23">
         <v>27.3</v>
       </c>
-      <c r="AC81" s="61">
+      <c r="AC81" s="45">
         <f>(AB81+AB82+AB83+AB84)/4</f>
         <v>23</v>
       </c>
@@ -7299,7 +7442,7 @@
       <c r="B82" s="6">
         <v>77</v>
       </c>
-      <c r="C82" s="48"/>
+      <c r="C82" s="52"/>
       <c r="D82" s="25" t="s">
         <v>89</v>
       </c>
@@ -7342,7 +7485,9 @@
         <v>1</v>
       </c>
       <c r="U82" s="23"/>
-      <c r="V82" s="23"/>
+      <c r="V82" s="29">
+        <v>1</v>
+      </c>
       <c r="W82" s="23"/>
       <c r="X82" s="23"/>
       <c r="Y82" s="23"/>
@@ -7351,18 +7496,18 @@
       </c>
       <c r="AA82" s="23">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB82" s="23">
         <v>15.5</v>
       </c>
-      <c r="AC82" s="61"/>
+      <c r="AC82" s="45"/>
     </row>
     <row r="83" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B83" s="6">
         <v>78</v>
       </c>
-      <c r="C83" s="48"/>
+      <c r="C83" s="52"/>
       <c r="D83" s="25" t="s">
         <v>88</v>
       </c>
@@ -7407,7 +7552,7 @@
         <v>1</v>
       </c>
       <c r="U83" s="23"/>
-      <c r="V83" s="39">
+      <c r="V83" s="18">
         <v>1</v>
       </c>
       <c r="W83" s="23"/>
@@ -7425,13 +7570,13 @@
       <c r="AB83" s="23">
         <v>24.6</v>
       </c>
-      <c r="AC83" s="61"/>
+      <c r="AC83" s="45"/>
     </row>
     <row r="84" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B84" s="6">
         <v>79</v>
       </c>
-      <c r="C84" s="48"/>
+      <c r="C84" s="52"/>
       <c r="D84" s="25" t="s">
         <v>87</v>
       </c>
@@ -7474,7 +7619,9 @@
       <c r="Q84" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="R84" s="23"/>
+      <c r="R84" s="42">
+        <v>1</v>
+      </c>
       <c r="S84" s="23" t="s">
         <v>1</v>
       </c>
@@ -7484,7 +7631,7 @@
       <c r="U84" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="V84" s="23">
+      <c r="V84" s="29">
         <v>1</v>
       </c>
       <c r="W84" s="23"/>
@@ -7497,18 +7644,18 @@
       </c>
       <c r="AA84" s="23">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB84" s="23">
         <v>24.6</v>
       </c>
-      <c r="AC84" s="61"/>
+      <c r="AC84" s="45"/>
     </row>
     <row r="85" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B85" s="18">
         <v>80</v>
       </c>
-      <c r="C85" s="45" t="s">
+      <c r="C85" s="47" t="s">
         <v>86</v>
       </c>
       <c r="D85" s="22" t="s">
@@ -7551,7 +7698,7 @@
       <c r="S85" s="18"/>
       <c r="T85" s="18"/>
       <c r="U85" s="18"/>
-      <c r="V85" s="39">
+      <c r="V85" s="18">
         <v>1</v>
       </c>
       <c r="W85" s="18"/>
@@ -7569,7 +7716,7 @@
       <c r="AB85" s="18">
         <v>24.6</v>
       </c>
-      <c r="AC85" s="60">
+      <c r="AC85" s="44">
         <f>(AB85+AB86+AB87+AB88)/4</f>
         <v>14.25</v>
       </c>
@@ -7578,7 +7725,7 @@
       <c r="B86" s="18">
         <v>81</v>
       </c>
-      <c r="C86" s="46"/>
+      <c r="C86" s="48"/>
       <c r="D86" s="20" t="s">
         <v>84</v>
       </c>
@@ -7617,7 +7764,9 @@
       <c r="U86" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V86" s="18"/>
+      <c r="V86" s="29">
+        <v>1</v>
+      </c>
       <c r="W86" s="18"/>
       <c r="X86" s="18"/>
       <c r="Y86" s="18"/>
@@ -7626,18 +7775,18 @@
       </c>
       <c r="AA86" s="18">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB86" s="18">
         <v>13.5</v>
       </c>
-      <c r="AC86" s="60"/>
+      <c r="AC86" s="44"/>
     </row>
     <row r="87" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B87" s="18">
         <v>82</v>
       </c>
-      <c r="C87" s="46"/>
+      <c r="C87" s="48"/>
       <c r="D87" s="20" t="s">
         <v>83</v>
       </c>
@@ -7676,7 +7825,9 @@
       <c r="U87" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V87" s="18"/>
+      <c r="V87" s="18">
+        <v>1</v>
+      </c>
       <c r="W87" s="18"/>
       <c r="X87" s="18"/>
       <c r="Y87" s="18"/>
@@ -7685,18 +7836,18 @@
       </c>
       <c r="AA87" s="18">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB87" s="18">
         <v>13.5</v>
       </c>
-      <c r="AC87" s="60"/>
+      <c r="AC87" s="44"/>
     </row>
     <row r="88" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="18">
         <v>83</v>
       </c>
-      <c r="C88" s="46"/>
+      <c r="C88" s="48"/>
       <c r="D88" s="20" t="s">
         <v>82</v>
       </c>
@@ -7725,7 +7876,9 @@
       <c r="S88" s="18"/>
       <c r="T88" s="18"/>
       <c r="U88" s="18"/>
-      <c r="V88" s="18"/>
+      <c r="V88" s="29">
+        <v>1</v>
+      </c>
       <c r="W88" s="18"/>
       <c r="X88" s="18"/>
       <c r="Y88" s="18"/>
@@ -7734,18 +7887,18 @@
       </c>
       <c r="AA88" s="18">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB88" s="18">
         <v>5.4</v>
       </c>
-      <c r="AC88" s="60"/>
+      <c r="AC88" s="44"/>
     </row>
     <row r="89" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B89" s="6">
         <v>84</v>
       </c>
-      <c r="C89" s="43" t="s">
+      <c r="C89" s="65" t="s">
         <v>81</v>
       </c>
       <c r="D89" s="17" t="s">
@@ -7790,7 +7943,7 @@
       <c r="S89" s="23"/>
       <c r="T89" s="23"/>
       <c r="U89" s="23"/>
-      <c r="V89" s="39">
+      <c r="V89" s="18">
         <v>1</v>
       </c>
       <c r="W89" s="23"/>
@@ -7806,7 +7959,7 @@
       <c r="AB89" s="23">
         <v>19.2</v>
       </c>
-      <c r="AC89" s="61">
+      <c r="AC89" s="45">
         <f>(AB89+AB90+AB91+AB92)/4</f>
         <v>16.850000000000001</v>
       </c>
@@ -7815,7 +7968,7 @@
       <c r="B90" s="6">
         <v>85</v>
       </c>
-      <c r="C90" s="44"/>
+      <c r="C90" s="66"/>
       <c r="D90" s="28" t="s">
         <v>79</v>
       </c>
@@ -7862,7 +8015,7 @@
       <c r="U90" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V90" s="23">
+      <c r="V90" s="29">
         <v>1</v>
       </c>
       <c r="W90" s="23"/>
@@ -7880,13 +8033,13 @@
       <c r="AB90" s="23">
         <v>24.6</v>
       </c>
-      <c r="AC90" s="61"/>
+      <c r="AC90" s="45"/>
     </row>
     <row r="91" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B91" s="6">
         <v>86</v>
       </c>
-      <c r="C91" s="44"/>
+      <c r="C91" s="66"/>
       <c r="D91" s="15" t="s">
         <v>78</v>
       </c>
@@ -7929,7 +8082,7 @@
       <c r="U91" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V91" s="23">
+      <c r="V91" s="18">
         <v>1</v>
       </c>
       <c r="W91" s="23"/>
@@ -7945,13 +8098,13 @@
       <c r="AB91" s="23">
         <v>8.1</v>
       </c>
-      <c r="AC91" s="61"/>
+      <c r="AC91" s="45"/>
     </row>
     <row r="92" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B92" s="6">
         <v>87</v>
       </c>
-      <c r="C92" s="44"/>
+      <c r="C92" s="66"/>
       <c r="D92" s="15" t="s">
         <v>77</v>
       </c>
@@ -7996,7 +8149,9 @@
       <c r="U92" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V92" s="23"/>
+      <c r="V92" s="29">
+        <v>1</v>
+      </c>
       <c r="W92" s="23"/>
       <c r="X92" s="23"/>
       <c r="Y92" s="23"/>
@@ -8005,18 +8160,18 @@
       </c>
       <c r="AA92" s="23">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB92" s="23">
         <v>15.5</v>
       </c>
-      <c r="AC92" s="61"/>
+      <c r="AC92" s="45"/>
     </row>
     <row r="93" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B93" s="6">
         <v>88</v>
       </c>
-      <c r="C93" s="45" t="s">
+      <c r="C93" s="47" t="s">
         <v>76</v>
       </c>
       <c r="D93" s="22" t="s">
@@ -8067,7 +8222,7 @@
         <v>1</v>
       </c>
       <c r="U93" s="18"/>
-      <c r="V93" s="39">
+      <c r="V93" s="29">
         <v>1</v>
       </c>
       <c r="W93" s="18"/>
@@ -8085,7 +8240,7 @@
       <c r="AB93" s="18">
         <v>30</v>
       </c>
-      <c r="AC93" s="60">
+      <c r="AC93" s="44">
         <f>(AB93+AB94+AB95+AB96)/4</f>
         <v>14.75</v>
       </c>
@@ -8094,7 +8249,7 @@
       <c r="B94" s="6">
         <v>89</v>
       </c>
-      <c r="C94" s="46"/>
+      <c r="C94" s="48"/>
       <c r="D94" s="20" t="s">
         <v>74</v>
       </c>
@@ -8133,7 +8288,7 @@
       <c r="S94" s="18"/>
       <c r="T94" s="18"/>
       <c r="U94" s="18"/>
-      <c r="V94" s="39">
+      <c r="V94" s="18">
         <v>1</v>
       </c>
       <c r="W94" s="18"/>
@@ -8151,13 +8306,13 @@
       <c r="AB94" s="18">
         <v>15.5</v>
       </c>
-      <c r="AC94" s="60"/>
+      <c r="AC94" s="44"/>
     </row>
     <row r="95" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="6">
         <v>90</v>
       </c>
-      <c r="C95" s="46"/>
+      <c r="C95" s="48"/>
       <c r="D95" s="20" t="s">
         <v>73</v>
       </c>
@@ -8188,7 +8343,9 @@
       <c r="S95" s="18"/>
       <c r="T95" s="18"/>
       <c r="U95" s="18"/>
-      <c r="V95" s="18"/>
+      <c r="V95" s="29">
+        <v>1</v>
+      </c>
       <c r="W95" s="18"/>
       <c r="X95" s="18"/>
       <c r="Y95" s="18"/>
@@ -8197,18 +8354,18 @@
       </c>
       <c r="AA95" s="18">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB95" s="18">
         <v>10.8</v>
       </c>
-      <c r="AC95" s="60"/>
+      <c r="AC95" s="44"/>
     </row>
     <row r="96" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B96" s="6">
         <v>91</v>
       </c>
-      <c r="C96" s="46"/>
+      <c r="C96" s="48"/>
       <c r="D96" s="20" t="s">
         <v>72</v>
       </c>
@@ -8235,7 +8392,9 @@
       <c r="S96" s="18"/>
       <c r="T96" s="18"/>
       <c r="U96" s="18"/>
-      <c r="V96" s="18"/>
+      <c r="V96" s="18">
+        <v>1</v>
+      </c>
       <c r="W96" s="18"/>
       <c r="X96" s="18"/>
       <c r="Y96" s="18"/>
@@ -8244,18 +8403,18 @@
       </c>
       <c r="AA96" s="18">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB96" s="18">
         <v>2.7</v>
       </c>
-      <c r="AC96" s="60"/>
+      <c r="AC96" s="44"/>
     </row>
     <row r="97" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B97" s="6">
         <v>92</v>
       </c>
-      <c r="C97" s="47" t="s">
+      <c r="C97" s="51" t="s">
         <v>71</v>
       </c>
       <c r="D97" s="27" t="s">
@@ -8312,7 +8471,7 @@
       <c r="U97" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V97" s="23">
+      <c r="V97" s="29">
         <v>1</v>
       </c>
       <c r="W97" s="23"/>
@@ -8330,7 +8489,7 @@
       <c r="AB97" s="23">
         <v>30</v>
       </c>
-      <c r="AC97" s="61">
+      <c r="AC97" s="45">
         <f>(AB97+AB98+AB99)/3</f>
         <v>24.266666666666666</v>
       </c>
@@ -8339,7 +8498,7 @@
       <c r="B98" s="6">
         <v>93</v>
       </c>
-      <c r="C98" s="48"/>
+      <c r="C98" s="52"/>
       <c r="D98" s="25" t="s">
         <v>69</v>
       </c>
@@ -8390,7 +8549,7 @@
       <c r="U98" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V98" s="23">
+      <c r="V98" s="18">
         <v>1</v>
       </c>
       <c r="W98" s="23"/>
@@ -8408,13 +8567,13 @@
       <c r="AB98" s="23">
         <v>27.3</v>
       </c>
-      <c r="AC98" s="61"/>
+      <c r="AC98" s="45"/>
     </row>
     <row r="99" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B99" s="6">
         <v>94</v>
       </c>
-      <c r="C99" s="48"/>
+      <c r="C99" s="52"/>
       <c r="D99" s="25" t="s">
         <v>68</v>
       </c>
@@ -8443,7 +8602,9 @@
       <c r="M99" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="N99" s="23"/>
+      <c r="N99" s="42">
+        <v>1</v>
+      </c>
       <c r="O99" s="33" t="s">
         <v>1</v>
       </c>
@@ -8463,7 +8624,9 @@
       <c r="U99" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V99" s="23"/>
+      <c r="V99" s="29">
+        <v>1</v>
+      </c>
       <c r="W99" s="23"/>
       <c r="X99" s="23">
         <v>1</v>
@@ -8474,18 +8637,18 @@
       </c>
       <c r="AA99" s="23">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB99" s="23">
         <v>15.5</v>
       </c>
-      <c r="AC99" s="61"/>
+      <c r="AC99" s="45"/>
     </row>
     <row r="100" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="6">
         <v>95</v>
       </c>
-      <c r="C100" s="45" t="s">
+      <c r="C100" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D100" s="22" t="s">
@@ -8518,7 +8681,9 @@
       <c r="S100" s="18"/>
       <c r="T100" s="18"/>
       <c r="U100" s="18"/>
-      <c r="V100" s="18"/>
+      <c r="V100" s="18">
+        <v>1</v>
+      </c>
       <c r="W100" s="18"/>
       <c r="X100" s="18"/>
       <c r="Y100" s="18"/>
@@ -8527,12 +8692,12 @@
       </c>
       <c r="AA100" s="18">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB100" s="18">
         <v>13.5</v>
       </c>
-      <c r="AC100" s="60">
+      <c r="AC100" s="44">
         <f>(AB100+AB101)/2</f>
         <v>8.1</v>
       </c>
@@ -8541,7 +8706,7 @@
       <c r="B101" s="6">
         <v>96</v>
       </c>
-      <c r="C101" s="46"/>
+      <c r="C101" s="48"/>
       <c r="D101" s="20" t="s">
         <v>65</v>
       </c>
@@ -8562,7 +8727,9 @@
       <c r="S101" s="18"/>
       <c r="T101" s="18"/>
       <c r="U101" s="18"/>
-      <c r="V101" s="18"/>
+      <c r="V101" s="29">
+        <v>1</v>
+      </c>
       <c r="W101" s="18"/>
       <c r="X101" s="18"/>
       <c r="Y101" s="18"/>
@@ -8571,18 +8738,18 @@
       </c>
       <c r="AA101" s="18">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB101" s="18">
         <v>2.7</v>
       </c>
-      <c r="AC101" s="60"/>
+      <c r="AC101" s="44"/>
     </row>
     <row r="102" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B102" s="6">
         <v>97</v>
       </c>
-      <c r="C102" s="47" t="s">
+      <c r="C102" s="51" t="s">
         <v>64</v>
       </c>
       <c r="D102" s="27" t="s">
@@ -8631,7 +8798,7 @@
       <c r="U102" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V102" s="23">
+      <c r="V102" s="18">
         <v>1</v>
       </c>
       <c r="W102" s="23"/>
@@ -8649,7 +8816,7 @@
       <c r="AB102" s="23">
         <v>24.6</v>
       </c>
-      <c r="AC102" s="61">
+      <c r="AC102" s="45">
         <f>(AB102+AB103+AB104+AB105)/4</f>
         <v>23.925000000000004</v>
       </c>
@@ -8658,7 +8825,7 @@
       <c r="B103" s="6">
         <v>98</v>
       </c>
-      <c r="C103" s="48"/>
+      <c r="C103" s="52"/>
       <c r="D103" s="25" t="s">
         <v>62</v>
       </c>
@@ -8703,7 +8870,7 @@
         <v>1</v>
       </c>
       <c r="U103" s="23"/>
-      <c r="V103" s="39">
+      <c r="V103" s="29">
         <v>1</v>
       </c>
       <c r="W103" s="23"/>
@@ -8721,13 +8888,13 @@
       <c r="AB103" s="23">
         <v>24.6</v>
       </c>
-      <c r="AC103" s="61"/>
+      <c r="AC103" s="45"/>
     </row>
     <row r="104" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B104" s="6">
         <v>99</v>
       </c>
-      <c r="C104" s="48"/>
+      <c r="C104" s="52"/>
       <c r="D104" s="25" t="s">
         <v>61</v>
       </c>
@@ -8774,7 +8941,7 @@
       <c r="U104" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V104" s="23">
+      <c r="V104" s="18">
         <v>1</v>
       </c>
       <c r="W104" s="23"/>
@@ -8792,13 +8959,13 @@
       <c r="AB104" s="23">
         <v>24.6</v>
       </c>
-      <c r="AC104" s="61"/>
+      <c r="AC104" s="45"/>
     </row>
     <row r="105" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B105" s="6">
         <v>100</v>
       </c>
-      <c r="C105" s="48"/>
+      <c r="C105" s="52"/>
       <c r="D105" s="25" t="s">
         <v>60</v>
       </c>
@@ -8843,7 +9010,7 @@
       <c r="U105" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V105" s="23">
+      <c r="V105" s="29">
         <v>1</v>
       </c>
       <c r="W105" s="23"/>
@@ -8861,13 +9028,13 @@
       <c r="AB105" s="23">
         <v>21.9</v>
       </c>
-      <c r="AC105" s="61"/>
+      <c r="AC105" s="45"/>
     </row>
     <row r="106" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B106" s="18">
         <v>101</v>
       </c>
-      <c r="C106" s="45" t="s">
+      <c r="C106" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D106" s="22" t="s">
@@ -8934,7 +9101,7 @@
       <c r="AB106" s="18">
         <v>24.6</v>
       </c>
-      <c r="AC106" s="60">
+      <c r="AC106" s="44">
         <f>(AB106+AB107+AB108+AB109)/4</f>
         <v>24.6</v>
       </c>
@@ -8943,7 +9110,7 @@
       <c r="B107" s="18">
         <v>102</v>
       </c>
-      <c r="C107" s="46"/>
+      <c r="C107" s="48"/>
       <c r="D107" s="20" t="s">
         <v>57</v>
       </c>
@@ -8990,7 +9157,9 @@
       <c r="U107" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V107" s="18"/>
+      <c r="V107" s="29">
+        <v>1</v>
+      </c>
       <c r="W107" s="18"/>
       <c r="X107" s="18">
         <v>1</v>
@@ -9001,19 +9170,19 @@
       </c>
       <c r="AA107" s="18">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB107" s="18">
         <v>21.9</v>
       </c>
-      <c r="AC107" s="60"/>
+      <c r="AC107" s="44"/>
     </row>
     <row r="108" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B108" s="18">
         <v>103</v>
       </c>
-      <c r="C108" s="46"/>
-      <c r="D108" s="20" t="s">
+      <c r="C108" s="48"/>
+      <c r="D108" s="25" t="s">
         <v>56</v>
       </c>
       <c r="E108" s="19" t="s">
@@ -9025,7 +9194,7 @@
       <c r="G108" s="18"/>
       <c r="H108" s="18"/>
       <c r="I108" s="18"/>
-      <c r="J108" s="39">
+      <c r="J108" s="42">
         <v>1</v>
       </c>
       <c r="K108" s="18" t="s">
@@ -9077,13 +9246,13 @@
       <c r="AB108" s="18">
         <v>27.3</v>
       </c>
-      <c r="AC108" s="60"/>
+      <c r="AC108" s="44"/>
     </row>
     <row r="109" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B109" s="18">
         <v>104</v>
       </c>
-      <c r="C109" s="46"/>
+      <c r="C109" s="48"/>
       <c r="D109" s="20" t="s">
         <v>55</v>
       </c>
@@ -9130,7 +9299,7 @@
       <c r="U109" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V109" s="18">
+      <c r="V109" s="29">
         <v>1</v>
       </c>
       <c r="W109" s="18"/>
@@ -9148,13 +9317,13 @@
       <c r="AB109" s="18">
         <v>24.6</v>
       </c>
-      <c r="AC109" s="60"/>
+      <c r="AC109" s="44"/>
     </row>
     <row r="110" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B110" s="6">
         <v>105</v>
       </c>
-      <c r="C110" s="47" t="s">
+      <c r="C110" s="51" t="s">
         <v>54</v>
       </c>
       <c r="D110" s="27" t="s">
@@ -9203,7 +9372,7 @@
       <c r="U110" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V110" s="23">
+      <c r="V110" s="18">
         <v>1</v>
       </c>
       <c r="W110" s="23"/>
@@ -9219,7 +9388,7 @@
       <c r="AB110" s="23">
         <v>15.5</v>
       </c>
-      <c r="AC110" s="61">
+      <c r="AC110" s="45">
         <f>(AB110+AB111+AB112)/3</f>
         <v>21.566666666666666</v>
       </c>
@@ -9228,7 +9397,7 @@
       <c r="B111" s="6">
         <v>106</v>
       </c>
-      <c r="C111" s="48"/>
+      <c r="C111" s="52"/>
       <c r="D111" s="25" t="s">
         <v>52</v>
       </c>
@@ -9238,7 +9407,9 @@
       <c r="F111" s="23">
         <v>1</v>
       </c>
-      <c r="G111" s="38"/>
+      <c r="G111" s="43" t="s">
+        <v>1</v>
+      </c>
       <c r="H111" s="23">
         <v>1</v>
       </c>
@@ -9279,7 +9450,7 @@
       <c r="U111" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V111" s="23">
+      <c r="V111" s="29">
         <v>1</v>
       </c>
       <c r="W111" s="23"/>
@@ -9295,13 +9466,13 @@
       <c r="AB111" s="23">
         <v>24.6</v>
       </c>
-      <c r="AC111" s="61"/>
+      <c r="AC111" s="45"/>
     </row>
     <row r="112" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B112" s="6">
         <v>107</v>
       </c>
-      <c r="C112" s="48"/>
+      <c r="C112" s="52"/>
       <c r="D112" s="25" t="s">
         <v>51</v>
       </c>
@@ -9354,7 +9525,7 @@
       <c r="U112" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V112" s="23">
+      <c r="V112" s="18">
         <v>1</v>
       </c>
       <c r="W112" s="23"/>
@@ -9370,13 +9541,13 @@
       <c r="AB112" s="23">
         <v>24.6</v>
       </c>
-      <c r="AC112" s="61"/>
+      <c r="AC112" s="45"/>
     </row>
     <row r="113" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="18">
         <v>108</v>
       </c>
-      <c r="C113" s="45" t="s">
+      <c r="C113" s="47" t="s">
         <v>50</v>
       </c>
       <c r="D113" s="22" t="s">
@@ -9407,7 +9578,9 @@
       <c r="S113" s="18"/>
       <c r="T113" s="18"/>
       <c r="U113" s="18"/>
-      <c r="V113" s="18"/>
+      <c r="V113" s="29">
+        <v>1</v>
+      </c>
       <c r="W113" s="18"/>
       <c r="X113" s="18"/>
       <c r="Y113" s="18"/>
@@ -9416,12 +9589,12 @@
       </c>
       <c r="AA113" s="18">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB113" s="18">
         <v>10.8</v>
       </c>
-      <c r="AC113" s="60">
+      <c r="AC113" s="44">
         <f>(AB113+AB114+AB115+AB116)/4</f>
         <v>6.0750000000000011</v>
       </c>
@@ -9430,7 +9603,7 @@
       <c r="B114" s="18">
         <v>109</v>
       </c>
-      <c r="C114" s="46"/>
+      <c r="C114" s="48"/>
       <c r="D114" s="20" t="s">
         <v>48</v>
       </c>
@@ -9455,7 +9628,9 @@
       <c r="S114" s="18"/>
       <c r="T114" s="18"/>
       <c r="U114" s="18"/>
-      <c r="V114" s="18"/>
+      <c r="V114" s="18">
+        <v>1</v>
+      </c>
       <c r="W114" s="18"/>
       <c r="X114" s="18"/>
       <c r="Y114" s="18"/>
@@ -9464,18 +9639,18 @@
       </c>
       <c r="AA114" s="18">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB114" s="18">
         <v>5.4</v>
       </c>
-      <c r="AC114" s="60"/>
+      <c r="AC114" s="44"/>
     </row>
     <row r="115" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="18">
         <v>110</v>
       </c>
-      <c r="C115" s="46"/>
+      <c r="C115" s="48"/>
       <c r="D115" s="20" t="s">
         <v>47</v>
       </c>
@@ -9496,7 +9671,9 @@
       <c r="S115" s="18"/>
       <c r="T115" s="18"/>
       <c r="U115" s="18"/>
-      <c r="V115" s="18"/>
+      <c r="V115" s="29">
+        <v>1</v>
+      </c>
       <c r="W115" s="18"/>
       <c r="X115" s="18"/>
       <c r="Y115" s="18"/>
@@ -9505,18 +9682,18 @@
       </c>
       <c r="AA115" s="18">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB115" s="18">
         <v>2.7</v>
       </c>
-      <c r="AC115" s="60"/>
+      <c r="AC115" s="44"/>
     </row>
     <row r="116" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="18">
         <v>111</v>
       </c>
-      <c r="C116" s="46"/>
+      <c r="C116" s="48"/>
       <c r="D116" s="20" t="s">
         <v>46</v>
       </c>
@@ -9539,7 +9716,9 @@
       <c r="S116" s="18"/>
       <c r="T116" s="18"/>
       <c r="U116" s="18"/>
-      <c r="V116" s="18"/>
+      <c r="V116" s="18">
+        <v>1</v>
+      </c>
       <c r="W116" s="18"/>
       <c r="X116" s="18"/>
       <c r="Y116" s="18"/>
@@ -9548,18 +9727,18 @@
       </c>
       <c r="AA116" s="18">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB116" s="18">
         <v>5.4</v>
       </c>
-      <c r="AC116" s="60"/>
+      <c r="AC116" s="44"/>
     </row>
     <row r="117" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B117" s="6">
         <v>112</v>
       </c>
-      <c r="C117" s="47" t="s">
+      <c r="C117" s="51" t="s">
         <v>45</v>
       </c>
       <c r="D117" s="27" t="s">
@@ -9614,7 +9793,7 @@
       <c r="U117" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V117" s="23">
+      <c r="V117" s="29">
         <v>1</v>
       </c>
       <c r="W117" s="23"/>
@@ -9632,7 +9811,7 @@
       <c r="AB117" s="23">
         <v>27.3</v>
       </c>
-      <c r="AC117" s="61">
+      <c r="AC117" s="45">
         <f>(AB117+AB118+AB119)/3</f>
         <v>26.400000000000002</v>
       </c>
@@ -9641,7 +9820,7 @@
       <c r="B118" s="6">
         <v>113</v>
       </c>
-      <c r="C118" s="48"/>
+      <c r="C118" s="52"/>
       <c r="D118" s="25" t="s">
         <v>43</v>
       </c>
@@ -9694,7 +9873,7 @@
       <c r="U118" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V118" s="23">
+      <c r="V118" s="29">
         <v>1</v>
       </c>
       <c r="W118" s="23"/>
@@ -9712,13 +9891,13 @@
       <c r="AB118" s="23">
         <v>27.3</v>
       </c>
-      <c r="AC118" s="61"/>
+      <c r="AC118" s="45"/>
     </row>
     <row r="119" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B119" s="6">
         <v>114</v>
       </c>
-      <c r="C119" s="48"/>
+      <c r="C119" s="52"/>
       <c r="D119" s="25" t="s">
         <v>42</v>
       </c>
@@ -9767,7 +9946,7 @@
       <c r="U119" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V119" s="23">
+      <c r="V119" s="18">
         <v>1</v>
       </c>
       <c r="W119" s="23"/>
@@ -9785,13 +9964,13 @@
       <c r="AB119" s="23">
         <v>24.6</v>
       </c>
-      <c r="AC119" s="61"/>
+      <c r="AC119" s="45"/>
     </row>
     <row r="120" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B120" s="18">
         <v>115</v>
       </c>
-      <c r="C120" s="45" t="s">
+      <c r="C120" s="47" t="s">
         <v>41</v>
       </c>
       <c r="D120" s="22" t="s">
@@ -9836,7 +10015,9 @@
         <v>1</v>
       </c>
       <c r="U120" s="18"/>
-      <c r="V120" s="18"/>
+      <c r="V120" s="29">
+        <v>1</v>
+      </c>
       <c r="W120" s="18"/>
       <c r="X120" s="18">
         <v>1</v>
@@ -9847,12 +10028,12 @@
       </c>
       <c r="AA120" s="18">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB120" s="18">
         <v>15.5</v>
       </c>
-      <c r="AC120" s="60">
+      <c r="AC120" s="44">
         <f>(AB120+AB121+AB122+AB123)/4</f>
         <v>10.625</v>
       </c>
@@ -9861,7 +10042,7 @@
       <c r="B121" s="18">
         <v>116</v>
       </c>
-      <c r="C121" s="46"/>
+      <c r="C121" s="48"/>
       <c r="D121" s="20" t="s">
         <v>39</v>
       </c>
@@ -9900,7 +10081,9 @@
       <c r="S121" s="18"/>
       <c r="T121" s="18"/>
       <c r="U121" s="18"/>
-      <c r="V121" s="18"/>
+      <c r="V121" s="18">
+        <v>1</v>
+      </c>
       <c r="W121" s="18"/>
       <c r="X121" s="18"/>
       <c r="Y121" s="18"/>
@@ -9909,18 +10092,18 @@
       </c>
       <c r="AA121" s="18">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB121" s="18">
         <v>13.5</v>
       </c>
-      <c r="AC121" s="60"/>
+      <c r="AC121" s="44"/>
     </row>
     <row r="122" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B122" s="18">
         <v>117</v>
       </c>
-      <c r="C122" s="46"/>
+      <c r="C122" s="48"/>
       <c r="D122" s="20" t="s">
         <v>38</v>
       </c>
@@ -9953,7 +10136,9 @@
       </c>
       <c r="T122" s="18"/>
       <c r="U122" s="18"/>
-      <c r="V122" s="18"/>
+      <c r="V122" s="29">
+        <v>1</v>
+      </c>
       <c r="W122" s="18"/>
       <c r="X122" s="18"/>
       <c r="Y122" s="18"/>
@@ -9962,18 +10147,18 @@
       </c>
       <c r="AA122" s="18">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB122" s="18">
         <v>8.1</v>
       </c>
-      <c r="AC122" s="60"/>
+      <c r="AC122" s="44"/>
     </row>
     <row r="123" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B123" s="18">
         <v>118</v>
       </c>
-      <c r="C123" s="46"/>
+      <c r="C123" s="48"/>
       <c r="D123" s="20" t="s">
         <v>37</v>
       </c>
@@ -9998,7 +10183,9 @@
       <c r="S123" s="18"/>
       <c r="T123" s="18"/>
       <c r="U123" s="18"/>
-      <c r="V123" s="18"/>
+      <c r="V123" s="18">
+        <v>1</v>
+      </c>
       <c r="W123" s="18"/>
       <c r="X123" s="18"/>
       <c r="Y123" s="18"/>
@@ -10007,18 +10194,18 @@
       </c>
       <c r="AA123" s="18">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB123" s="18">
         <v>5.4</v>
       </c>
-      <c r="AC123" s="60"/>
+      <c r="AC123" s="44"/>
     </row>
     <row r="124" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B124" s="6">
         <v>119</v>
       </c>
-      <c r="C124" s="47" t="s">
+      <c r="C124" s="51" t="s">
         <v>36</v>
       </c>
       <c r="D124" s="27" t="s">
@@ -10055,7 +10242,7 @@
       <c r="U124" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V124" s="23">
+      <c r="V124" s="29">
         <v>1</v>
       </c>
       <c r="W124" s="23"/>
@@ -10071,7 +10258,7 @@
       <c r="AB124" s="23">
         <v>13.5</v>
       </c>
-      <c r="AC124" s="61">
+      <c r="AC124" s="45">
         <f>(AB124+AB125)/2</f>
         <v>12.15</v>
       </c>
@@ -10080,7 +10267,7 @@
       <c r="B125" s="6">
         <v>120</v>
       </c>
-      <c r="C125" s="48"/>
+      <c r="C125" s="52"/>
       <c r="D125" s="25" t="s">
         <v>34</v>
       </c>
@@ -10115,7 +10302,9 @@
       <c r="U125" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V125" s="23"/>
+      <c r="V125" s="18">
+        <v>1</v>
+      </c>
       <c r="W125" s="23"/>
       <c r="X125" s="23"/>
       <c r="Y125" s="23"/>
@@ -10124,18 +10313,18 @@
       </c>
       <c r="AA125" s="23">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB125" s="23">
         <v>10.8</v>
       </c>
-      <c r="AC125" s="61"/>
+      <c r="AC125" s="45"/>
     </row>
     <row r="126" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B126" s="18">
         <v>121</v>
       </c>
-      <c r="C126" s="45" t="s">
+      <c r="C126" s="47" t="s">
         <v>33</v>
       </c>
       <c r="D126" s="22" t="s">
@@ -10190,7 +10379,7 @@
       <c r="U126" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V126" s="18">
+      <c r="V126" s="29">
         <v>1</v>
       </c>
       <c r="W126" s="18"/>
@@ -10208,7 +10397,7 @@
       <c r="AB126" s="18">
         <v>30</v>
       </c>
-      <c r="AC126" s="60">
+      <c r="AC126" s="44">
         <f>(AB126+AB127)/2</f>
         <v>30</v>
       </c>
@@ -10217,7 +10406,7 @@
       <c r="B127" s="18">
         <v>122</v>
       </c>
-      <c r="C127" s="46"/>
+      <c r="C127" s="48"/>
       <c r="D127" s="20" t="s">
         <v>31</v>
       </c>
@@ -10290,13 +10479,13 @@
       <c r="AB127" s="18">
         <v>30</v>
       </c>
-      <c r="AC127" s="60"/>
+      <c r="AC127" s="44"/>
     </row>
     <row r="128" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B128" s="6">
         <v>123</v>
       </c>
-      <c r="C128" s="47" t="s">
+      <c r="C128" s="51" t="s">
         <v>30</v>
       </c>
       <c r="D128" s="27" t="s">
@@ -10339,7 +10528,7 @@
       <c r="U128" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V128" s="23">
+      <c r="V128" s="29">
         <v>1</v>
       </c>
       <c r="W128" s="23"/>
@@ -10355,7 +10544,7 @@
       <c r="AB128" s="23">
         <v>13.5</v>
       </c>
-      <c r="AC128" s="61">
+      <c r="AC128" s="45">
         <f>(AB128+AB129+AB130+AB131)/4</f>
         <v>8.1000000000000014</v>
       </c>
@@ -10364,7 +10553,7 @@
       <c r="B129" s="6">
         <v>124</v>
       </c>
-      <c r="C129" s="48"/>
+      <c r="C129" s="52"/>
       <c r="D129" s="25" t="s">
         <v>28</v>
       </c>
@@ -10403,7 +10592,9 @@
       <c r="U129" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V129" s="23"/>
+      <c r="V129" s="18">
+        <v>1</v>
+      </c>
       <c r="W129" s="23"/>
       <c r="X129" s="23"/>
       <c r="Y129" s="23"/>
@@ -10412,18 +10603,18 @@
       </c>
       <c r="AA129" s="23">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB129" s="23">
         <v>8.1</v>
       </c>
-      <c r="AC129" s="61"/>
+      <c r="AC129" s="45"/>
     </row>
     <row r="130" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B130" s="6">
         <v>125</v>
       </c>
-      <c r="C130" s="48"/>
+      <c r="C130" s="52"/>
       <c r="D130" s="25" t="s">
         <v>27</v>
       </c>
@@ -10460,7 +10651,7 @@
       <c r="U130" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V130" s="23">
+      <c r="V130" s="29">
         <v>1</v>
       </c>
       <c r="W130" s="23"/>
@@ -10476,13 +10667,13 @@
       <c r="AB130" s="23">
         <v>8.1</v>
       </c>
-      <c r="AC130" s="61"/>
+      <c r="AC130" s="45"/>
     </row>
     <row r="131" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B131" s="6">
         <v>126</v>
       </c>
-      <c r="C131" s="48"/>
+      <c r="C131" s="52"/>
       <c r="D131" s="25" t="s">
         <v>26</v>
       </c>
@@ -10515,7 +10706,9 @@
       <c r="U131" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V131" s="23"/>
+      <c r="V131" s="18">
+        <v>1</v>
+      </c>
       <c r="W131" s="23"/>
       <c r="X131" s="23"/>
       <c r="Y131" s="23"/>
@@ -10524,18 +10717,18 @@
       </c>
       <c r="AA131" s="23">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB131" s="23">
         <v>2.7</v>
       </c>
-      <c r="AC131" s="61"/>
+      <c r="AC131" s="45"/>
     </row>
     <row r="132" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="18">
         <v>127</v>
       </c>
-      <c r="C132" s="45" t="s">
+      <c r="C132" s="47" t="s">
         <v>25</v>
       </c>
       <c r="D132" s="22" t="s">
@@ -10560,7 +10753,9 @@
       <c r="S132" s="18"/>
       <c r="T132" s="18"/>
       <c r="U132" s="18"/>
-      <c r="V132" s="18"/>
+      <c r="V132" s="29">
+        <v>1</v>
+      </c>
       <c r="W132" s="18"/>
       <c r="X132" s="18"/>
       <c r="Y132" s="18"/>
@@ -10569,12 +10764,12 @@
       </c>
       <c r="AA132" s="18">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB132" s="18">
         <v>5.4</v>
       </c>
-      <c r="AC132" s="60">
+      <c r="AC132" s="44">
         <f>(AB132+AB133+AB134+AB135)/4</f>
         <v>4.0500000000000007</v>
       </c>
@@ -10583,7 +10778,7 @@
       <c r="B133" s="18">
         <v>128</v>
       </c>
-      <c r="C133" s="46"/>
+      <c r="C133" s="48"/>
       <c r="D133" s="20" t="s">
         <v>23</v>
       </c>
@@ -10604,7 +10799,9 @@
       <c r="S133" s="18"/>
       <c r="T133" s="18"/>
       <c r="U133" s="18"/>
-      <c r="V133" s="18"/>
+      <c r="V133" s="18">
+        <v>1</v>
+      </c>
       <c r="W133" s="18"/>
       <c r="X133" s="18"/>
       <c r="Y133" s="18"/>
@@ -10613,18 +10810,18 @@
       </c>
       <c r="AA133" s="18">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB133" s="18">
         <v>2.7</v>
       </c>
-      <c r="AC133" s="60"/>
+      <c r="AC133" s="44"/>
     </row>
     <row r="134" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B134" s="18">
         <v>129</v>
       </c>
-      <c r="C134" s="46"/>
+      <c r="C134" s="48"/>
       <c r="D134" s="20" t="s">
         <v>22</v>
       </c>
@@ -10647,7 +10844,9 @@
       <c r="S134" s="18"/>
       <c r="T134" s="18"/>
       <c r="U134" s="18"/>
-      <c r="V134" s="18"/>
+      <c r="V134" s="29">
+        <v>1</v>
+      </c>
       <c r="W134" s="18"/>
       <c r="X134" s="18"/>
       <c r="Y134" s="18"/>
@@ -10656,18 +10855,18 @@
       </c>
       <c r="AA134" s="18">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB134" s="18">
         <v>5.4</v>
       </c>
-      <c r="AC134" s="60"/>
+      <c r="AC134" s="44"/>
     </row>
     <row r="135" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="18">
         <v>130</v>
       </c>
-      <c r="C135" s="46"/>
+      <c r="C135" s="48"/>
       <c r="D135" s="20" t="s">
         <v>21</v>
       </c>
@@ -10688,7 +10887,9 @@
       <c r="S135" s="18"/>
       <c r="T135" s="18"/>
       <c r="U135" s="18"/>
-      <c r="V135" s="18"/>
+      <c r="V135" s="18">
+        <v>1</v>
+      </c>
       <c r="W135" s="18"/>
       <c r="X135" s="18"/>
       <c r="Y135" s="18"/>
@@ -10697,18 +10898,18 @@
       </c>
       <c r="AA135" s="18">
         <f t="shared" ref="AA135:AA150" si="2">COUNT(Z135,X135,V135,T135,R135,P135,N135,L135,J135,H135,F135)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB135" s="18">
         <v>2.7</v>
       </c>
-      <c r="AC135" s="60"/>
+      <c r="AC135" s="44"/>
     </row>
     <row r="136" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B136" s="6">
         <v>131</v>
       </c>
-      <c r="C136" s="47" t="s">
+      <c r="C136" s="51" t="s">
         <v>20</v>
       </c>
       <c r="D136" s="27" t="s">
@@ -10747,7 +10948,9 @@
         <v>1</v>
       </c>
       <c r="U136" s="23"/>
-      <c r="V136" s="23"/>
+      <c r="V136" s="29">
+        <v>1</v>
+      </c>
       <c r="W136" s="23"/>
       <c r="X136" s="23"/>
       <c r="Y136" s="23"/>
@@ -10756,12 +10959,12 @@
       </c>
       <c r="AA136" s="23">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB136" s="23">
         <v>10.8</v>
       </c>
-      <c r="AC136" s="61">
+      <c r="AC136" s="45">
         <f>(AB136+AB137+AB138+AB139)/4</f>
         <v>7.4249999999999998</v>
       </c>
@@ -10770,7 +10973,7 @@
       <c r="B137" s="6">
         <v>132</v>
       </c>
-      <c r="C137" s="48"/>
+      <c r="C137" s="52"/>
       <c r="D137" s="25" t="s">
         <v>18</v>
       </c>
@@ -10807,7 +11010,9 @@
       </c>
       <c r="T137" s="23"/>
       <c r="U137" s="23"/>
-      <c r="V137" s="23"/>
+      <c r="V137" s="18">
+        <v>1</v>
+      </c>
       <c r="W137" s="23"/>
       <c r="X137" s="23"/>
       <c r="Y137" s="23"/>
@@ -10816,18 +11021,18 @@
       </c>
       <c r="AA137" s="23">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB137" s="23">
         <v>10.8</v>
       </c>
-      <c r="AC137" s="61"/>
+      <c r="AC137" s="45"/>
     </row>
     <row r="138" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B138" s="6">
         <v>133</v>
       </c>
-      <c r="C138" s="48"/>
+      <c r="C138" s="52"/>
       <c r="D138" s="25" t="s">
         <v>17</v>
       </c>
@@ -10860,7 +11065,9 @@
       </c>
       <c r="T138" s="23"/>
       <c r="U138" s="23"/>
-      <c r="V138" s="23"/>
+      <c r="V138" s="29">
+        <v>1</v>
+      </c>
       <c r="W138" s="23"/>
       <c r="X138" s="23"/>
       <c r="Y138" s="23"/>
@@ -10869,18 +11076,18 @@
       </c>
       <c r="AA138" s="23">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB138" s="23">
         <v>5.4</v>
       </c>
-      <c r="AC138" s="61"/>
+      <c r="AC138" s="45"/>
     </row>
     <row r="139" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B139" s="6">
         <v>134</v>
       </c>
-      <c r="C139" s="48"/>
+      <c r="C139" s="52"/>
       <c r="D139" s="25" t="s">
         <v>16</v>
       </c>
@@ -10905,7 +11112,9 @@
       <c r="S139" s="23"/>
       <c r="T139" s="23"/>
       <c r="U139" s="23"/>
-      <c r="V139" s="23"/>
+      <c r="V139" s="18">
+        <v>1</v>
+      </c>
       <c r="W139" s="23"/>
       <c r="X139" s="23"/>
       <c r="Y139" s="23"/>
@@ -10914,18 +11123,18 @@
       </c>
       <c r="AA139" s="23">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB139" s="23">
         <v>2.7</v>
       </c>
-      <c r="AC139" s="61"/>
+      <c r="AC139" s="45"/>
     </row>
     <row r="140" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B140" s="18">
         <v>135</v>
       </c>
-      <c r="C140" s="45" t="s">
+      <c r="C140" s="47" t="s">
         <v>15</v>
       </c>
       <c r="D140" s="22" t="s">
@@ -10964,7 +11173,9 @@
       </c>
       <c r="T140" s="18"/>
       <c r="U140" s="18"/>
-      <c r="V140" s="18"/>
+      <c r="V140" s="29">
+        <v>1</v>
+      </c>
       <c r="W140" s="18"/>
       <c r="X140" s="18"/>
       <c r="Y140" s="18"/>
@@ -10973,12 +11184,12 @@
       </c>
       <c r="AA140" s="18">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB140" s="18">
         <v>8.1</v>
       </c>
-      <c r="AC140" s="60">
+      <c r="AC140" s="44">
         <f>(AB140+AB141)/2</f>
         <v>10.8</v>
       </c>
@@ -10987,7 +11198,7 @@
       <c r="B141" s="18">
         <v>136</v>
       </c>
-      <c r="C141" s="46"/>
+      <c r="C141" s="48"/>
       <c r="D141" s="20" t="s">
         <v>13</v>
       </c>
@@ -11026,7 +11237,7 @@
         <v>1</v>
       </c>
       <c r="U141" s="18"/>
-      <c r="V141" s="39">
+      <c r="V141" s="18">
         <v>1</v>
       </c>
       <c r="W141" s="18"/>
@@ -11042,13 +11253,13 @@
       <c r="AB141" s="18">
         <v>13.5</v>
       </c>
-      <c r="AC141" s="60"/>
+      <c r="AC141" s="44"/>
     </row>
     <row r="142" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B142" s="6">
         <v>137</v>
       </c>
-      <c r="C142" s="47" t="s">
+      <c r="C142" s="51" t="s">
         <v>12</v>
       </c>
       <c r="D142" s="27" t="s">
@@ -11101,7 +11312,7 @@
       <c r="U142" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="V142" s="23">
+      <c r="V142" s="29">
         <v>1</v>
       </c>
       <c r="W142" s="23"/>
@@ -11119,7 +11330,7 @@
       <c r="AB142" s="23">
         <v>27.3</v>
       </c>
-      <c r="AC142" s="61">
+      <c r="AC142" s="45">
         <f>(AB142+AB143)/2</f>
         <v>19.05</v>
       </c>
@@ -11128,7 +11339,7 @@
       <c r="B143" s="6">
         <v>138</v>
       </c>
-      <c r="C143" s="48"/>
+      <c r="C143" s="52"/>
       <c r="D143" s="25" t="s">
         <v>10</v>
       </c>
@@ -11173,7 +11384,9 @@
       <c r="U143" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V143" s="23"/>
+      <c r="V143" s="18">
+        <v>1</v>
+      </c>
       <c r="W143" s="23"/>
       <c r="X143" s="23"/>
       <c r="Y143" s="23"/>
@@ -11182,18 +11395,18 @@
       </c>
       <c r="AA143" s="23">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB143" s="23">
         <v>10.8</v>
       </c>
-      <c r="AC143" s="61"/>
+      <c r="AC143" s="45"/>
     </row>
     <row r="144" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B144" s="18">
         <v>139</v>
       </c>
-      <c r="C144" s="45" t="s">
+      <c r="C144" s="47" t="s">
         <v>9</v>
       </c>
       <c r="D144" s="22" t="s">
@@ -11220,7 +11433,7 @@
       <c r="S144" s="18"/>
       <c r="T144" s="18"/>
       <c r="U144" s="18"/>
-      <c r="V144" s="39">
+      <c r="V144" s="29">
         <v>1</v>
       </c>
       <c r="W144" s="18"/>
@@ -11236,7 +11449,7 @@
       <c r="AB144" s="18">
         <v>8.1</v>
       </c>
-      <c r="AC144" s="60">
+      <c r="AC144" s="44">
         <f>(AB144+AB145)/2</f>
         <v>5.4</v>
       </c>
@@ -11245,7 +11458,7 @@
       <c r="B145" s="18">
         <v>140</v>
       </c>
-      <c r="C145" s="46"/>
+      <c r="C145" s="48"/>
       <c r="D145" s="20" t="s">
         <v>7</v>
       </c>
@@ -11266,7 +11479,9 @@
       <c r="S145" s="18"/>
       <c r="T145" s="18"/>
       <c r="U145" s="18"/>
-      <c r="V145" s="18"/>
+      <c r="V145" s="29">
+        <v>1</v>
+      </c>
       <c r="W145" s="18"/>
       <c r="X145" s="18"/>
       <c r="Y145" s="18"/>
@@ -11275,18 +11490,18 @@
       </c>
       <c r="AA145" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB145" s="18">
         <v>2.7</v>
       </c>
-      <c r="AC145" s="60"/>
+      <c r="AC145" s="44"/>
     </row>
     <row r="146" spans="2:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B146" s="6">
         <v>141</v>
       </c>
-      <c r="C146" s="43" t="s">
+      <c r="C146" s="65" t="s">
         <v>6</v>
       </c>
       <c r="D146" s="17" t="s">
@@ -11309,7 +11524,9 @@
       <c r="S146" s="6"/>
       <c r="T146" s="6"/>
       <c r="U146" s="6"/>
-      <c r="V146" s="6"/>
+      <c r="V146" s="18">
+        <v>1</v>
+      </c>
       <c r="W146" s="6"/>
       <c r="X146" s="6"/>
       <c r="Y146" s="6"/>
@@ -11318,12 +11535,12 @@
       </c>
       <c r="AA146" s="6">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB146" s="6">
         <v>2.7</v>
       </c>
-      <c r="AC146" s="61">
+      <c r="AC146" s="45">
         <f>(AB146+AB147)/2</f>
         <v>2.7</v>
       </c>
@@ -11332,7 +11549,7 @@
       <c r="B147" s="6">
         <v>142</v>
       </c>
-      <c r="C147" s="44"/>
+      <c r="C147" s="66"/>
       <c r="D147" s="15" t="s">
         <v>4</v>
       </c>
@@ -11353,7 +11570,9 @@
       <c r="S147" s="6"/>
       <c r="T147" s="6"/>
       <c r="U147" s="6"/>
-      <c r="V147" s="6"/>
+      <c r="V147" s="29">
+        <v>1</v>
+      </c>
       <c r="W147" s="6"/>
       <c r="X147" s="6"/>
       <c r="Y147" s="6"/>
@@ -11362,12 +11581,12 @@
       </c>
       <c r="AA147" s="6">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB147" s="6">
         <v>2.7</v>
       </c>
-      <c r="AC147" s="61"/>
+      <c r="AC147" s="45"/>
     </row>
     <row r="148" spans="2:29" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B148" s="13"/>
@@ -11424,7 +11643,9 @@
       <c r="S149" s="6"/>
       <c r="T149" s="6"/>
       <c r="U149" s="6"/>
-      <c r="V149" s="6"/>
+      <c r="V149" s="6">
+        <v>1</v>
+      </c>
       <c r="W149" s="6"/>
       <c r="X149" s="6"/>
       <c r="Y149" s="6"/>
@@ -11433,7 +11654,7 @@
       </c>
       <c r="AA149" s="6">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB149" s="6">
         <v>5.4</v>
@@ -11465,7 +11686,9 @@
       <c r="S150" s="6"/>
       <c r="T150" s="6"/>
       <c r="U150" s="6"/>
-      <c r="V150" s="6"/>
+      <c r="V150" s="6">
+        <v>1</v>
+      </c>
       <c r="W150" s="6"/>
       <c r="X150" s="6"/>
       <c r="Y150" s="6"/>
@@ -11474,7 +11697,7 @@
       </c>
       <c r="AA150" s="6">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB150" s="5">
         <v>5.4</v>
@@ -11488,52 +11711,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="2:29" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="2:29" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="2:29" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="2:29" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="2:29" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="2:29" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="2:29" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="161" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="162" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="163" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="164" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="114">
-    <mergeCell ref="AC140:AC141"/>
-    <mergeCell ref="AC142:AC143"/>
-    <mergeCell ref="AC144:AC145"/>
-    <mergeCell ref="AC146:AC147"/>
-    <mergeCell ref="AC124:AC125"/>
-    <mergeCell ref="AC126:AC127"/>
-    <mergeCell ref="AC128:AC131"/>
-    <mergeCell ref="AC132:AC135"/>
-    <mergeCell ref="AC136:AC139"/>
-    <mergeCell ref="AC106:AC109"/>
-    <mergeCell ref="AC110:AC112"/>
-    <mergeCell ref="AC113:AC116"/>
-    <mergeCell ref="AC117:AC119"/>
-    <mergeCell ref="AC120:AC123"/>
-    <mergeCell ref="AC89:AC92"/>
-    <mergeCell ref="AC93:AC96"/>
-    <mergeCell ref="AC97:AC99"/>
-    <mergeCell ref="AC100:AC101"/>
-    <mergeCell ref="AC102:AC105"/>
-    <mergeCell ref="AC6:AC7"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AC41:AC43"/>
-    <mergeCell ref="AC44:AC46"/>
-    <mergeCell ref="AC72:AC75"/>
-    <mergeCell ref="AC76:AC78"/>
-    <mergeCell ref="AC79:AC80"/>
-    <mergeCell ref="AC81:AC84"/>
-    <mergeCell ref="AC85:AC88"/>
-    <mergeCell ref="AC55:AC58"/>
-    <mergeCell ref="AC59:AC62"/>
-    <mergeCell ref="AC63:AC65"/>
-    <mergeCell ref="AC66:AC69"/>
-    <mergeCell ref="AC70:AC71"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="C146:C147"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C89:C92"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="C85:C88"/>
+    <mergeCell ref="C93:C96"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="C128:C131"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="C132:C135"/>
+    <mergeCell ref="C136:C139"/>
+    <mergeCell ref="C110:C112"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="C37:C40"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="W3:Z3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C120:C123"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="O3:T3"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="C117:C119"/>
+    <mergeCell ref="C113:C116"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="C55:C58"/>
     <mergeCell ref="C140:C141"/>
     <mergeCell ref="O4:P4"/>
     <mergeCell ref="C70:C71"/>
@@ -11558,63 +11794,39 @@
     <mergeCell ref="AC37:AC40"/>
     <mergeCell ref="AA3:AA5"/>
     <mergeCell ref="AB3:AC4"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="C117:C119"/>
-    <mergeCell ref="C113:C116"/>
-    <mergeCell ref="C47:C50"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="C55:C58"/>
-    <mergeCell ref="W3:Z3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C120:C123"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="C72:C75"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C81:C84"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="O3:T3"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C89:C92"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="C85:C88"/>
-    <mergeCell ref="C93:C96"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="C128:C131"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="C132:C135"/>
-    <mergeCell ref="C136:C139"/>
-    <mergeCell ref="C110:C112"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="C37:C40"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="AC6:AC7"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AC41:AC43"/>
+    <mergeCell ref="AC44:AC46"/>
+    <mergeCell ref="AC72:AC75"/>
+    <mergeCell ref="AC76:AC78"/>
+    <mergeCell ref="AC79:AC80"/>
+    <mergeCell ref="AC81:AC84"/>
+    <mergeCell ref="AC85:AC88"/>
+    <mergeCell ref="AC55:AC58"/>
+    <mergeCell ref="AC59:AC62"/>
+    <mergeCell ref="AC63:AC65"/>
+    <mergeCell ref="AC66:AC69"/>
+    <mergeCell ref="AC70:AC71"/>
+    <mergeCell ref="AC106:AC109"/>
+    <mergeCell ref="AC110:AC112"/>
+    <mergeCell ref="AC113:AC116"/>
+    <mergeCell ref="AC117:AC119"/>
+    <mergeCell ref="AC120:AC123"/>
+    <mergeCell ref="AC89:AC92"/>
+    <mergeCell ref="AC93:AC96"/>
+    <mergeCell ref="AC97:AC99"/>
+    <mergeCell ref="AC100:AC101"/>
+    <mergeCell ref="AC102:AC105"/>
+    <mergeCell ref="AC140:AC141"/>
+    <mergeCell ref="AC142:AC143"/>
+    <mergeCell ref="AC144:AC145"/>
+    <mergeCell ref="AC146:AC147"/>
+    <mergeCell ref="AC124:AC125"/>
+    <mergeCell ref="AC126:AC127"/>
+    <mergeCell ref="AC128:AC131"/>
+    <mergeCell ref="AC132:AC135"/>
+    <mergeCell ref="AC136:AC139"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
